--- a/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>IX</t>
   </si>
@@ -656,401 +656,413 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4533500</v>
+        <v>4570600</v>
       </c>
       <c r="E8" s="3">
-        <v>4495100</v>
+        <v>4601800</v>
       </c>
       <c r="F8" s="3">
-        <v>4459000</v>
+        <v>4562800</v>
       </c>
       <c r="G8" s="3">
-        <v>4183400</v>
+        <v>4526100</v>
       </c>
       <c r="H8" s="3">
-        <v>4694500</v>
+        <v>4246400</v>
       </c>
       <c r="I8" s="3">
-        <v>4367900</v>
+        <v>4765200</v>
       </c>
       <c r="J8" s="3">
+        <v>4433700</v>
+      </c>
+      <c r="K8" s="3">
         <v>4331000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4304600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4561900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4474800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4445500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4258400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4261900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4586100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5250300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5208200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5394500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5023800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6138000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5042300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6113700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5489600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6037700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6120900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6558500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7162400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6678100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6250200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5616300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2613900</v>
+        <v>2519900</v>
       </c>
       <c r="E9" s="3">
-        <v>2638100</v>
+        <v>2653300</v>
       </c>
       <c r="F9" s="3">
-        <v>2695300</v>
+        <v>2677800</v>
       </c>
       <c r="G9" s="3">
-        <v>2302800</v>
+        <v>2735900</v>
       </c>
       <c r="H9" s="3">
-        <v>3105300</v>
+        <v>2332300</v>
       </c>
       <c r="I9" s="3">
-        <v>2774700</v>
+        <v>3152100</v>
       </c>
       <c r="J9" s="3">
+        <v>2816500</v>
+      </c>
+      <c r="K9" s="3">
         <v>2792900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2639600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2863300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2678900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2911600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2651900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2623600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2965900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3323400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3188900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3275300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2984300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3960200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3109200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3952000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3459500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4148400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4173600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4727200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5316600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4878500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4517300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3914700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1919600</v>
+        <v>2050700</v>
       </c>
       <c r="E10" s="3">
-        <v>1857000</v>
+        <v>1948500</v>
       </c>
       <c r="F10" s="3">
-        <v>1763700</v>
+        <v>1885000</v>
       </c>
       <c r="G10" s="3">
-        <v>1880600</v>
+        <v>1790200</v>
       </c>
       <c r="H10" s="3">
-        <v>1589200</v>
+        <v>1914100</v>
       </c>
       <c r="I10" s="3">
-        <v>1593200</v>
+        <v>1613100</v>
       </c>
       <c r="J10" s="3">
+        <v>1617200</v>
+      </c>
+      <c r="K10" s="3">
         <v>1538100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1665000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1698700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1795800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1534000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1606500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1638300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1620200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1926900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2019300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2119200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2039500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2177800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1933100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2161700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2030100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1889300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1947200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1831300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1845700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1799600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1732900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1701600</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1083,8 +1095,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,8 +1188,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1267,192 +1283,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
-        <v>2200</v>
-      </c>
       <c r="G14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H14" s="3">
         <v>3600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>136800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>102900</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-35000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>22500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>4700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>23000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>22600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>14100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>9800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>38400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>30100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F15" s="3">
+        <v>14300</v>
+      </c>
+      <c r="G15" s="3">
+        <v>12200</v>
+      </c>
+      <c r="H15" s="3">
+        <v>14900</v>
+      </c>
+      <c r="I15" s="3">
+        <v>14700</v>
+      </c>
+      <c r="J15" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K15" s="3">
+        <v>15400</v>
+      </c>
+      <c r="L15" s="3">
+        <v>16000</v>
+      </c>
+      <c r="M15" s="3">
+        <v>14800</v>
+      </c>
+      <c r="N15" s="3">
+        <v>17500</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3">
         <v>15100</v>
       </c>
-      <c r="E15" s="3">
-        <v>14100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>12000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>14700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>14500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>14400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>15400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>16000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>14800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>17500</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="3">
-        <v>15100</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>16500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>16700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>20100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>17200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>16400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>16200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>13200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>12500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>10500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>9900</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC15" s="3">
         <v>11400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>11000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>13300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>11900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1482,192 +1507,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3997100</v>
+        <v>3922400</v>
       </c>
       <c r="E17" s="3">
-        <v>3942300</v>
+        <v>4057300</v>
       </c>
       <c r="F17" s="3">
-        <v>3948800</v>
+        <v>4001700</v>
       </c>
       <c r="G17" s="3">
-        <v>3591100</v>
+        <v>4008200</v>
       </c>
       <c r="H17" s="3">
-        <v>4249200</v>
+        <v>3640000</v>
       </c>
       <c r="I17" s="3">
-        <v>3811200</v>
+        <v>4313200</v>
       </c>
       <c r="J17" s="3">
+        <v>3868600</v>
+      </c>
+      <c r="K17" s="3">
         <v>4198400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3801700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3790900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3725200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3979600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3717000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3682900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4160600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4960500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4524800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4603700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4330800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5453200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4446700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5155900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4653400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5469000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5359200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5681200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6330900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5953800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5529800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4916200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>536400</v>
+        <v>648100</v>
       </c>
       <c r="E18" s="3">
-        <v>552800</v>
+        <v>544500</v>
       </c>
       <c r="F18" s="3">
-        <v>510200</v>
+        <v>561100</v>
       </c>
       <c r="G18" s="3">
-        <v>592200</v>
+        <v>517900</v>
       </c>
       <c r="H18" s="3">
-        <v>445300</v>
+        <v>606400</v>
       </c>
       <c r="I18" s="3">
-        <v>556700</v>
+        <v>452000</v>
       </c>
       <c r="J18" s="3">
+        <v>565100</v>
+      </c>
+      <c r="K18" s="3">
         <v>132600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>502900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>771000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>749500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>465900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>541400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>579000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>425500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>289800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>683400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>790800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>693000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>684800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>595600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>957800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>836200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>568700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>761700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>877300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>831500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>724300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>720400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>700100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1700,192 +1732,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>94900</v>
+        <v>198000</v>
       </c>
       <c r="E20" s="3">
-        <v>40800</v>
+        <v>96300</v>
       </c>
       <c r="F20" s="3">
-        <v>45500</v>
+        <v>41400</v>
       </c>
       <c r="G20" s="3">
-        <v>198800</v>
+        <v>46200</v>
       </c>
       <c r="H20" s="3">
-        <v>89600</v>
+        <v>201800</v>
       </c>
       <c r="I20" s="3">
-        <v>11400</v>
+        <v>90900</v>
       </c>
       <c r="J20" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K20" s="3">
         <v>1117000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>155900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>99500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-14100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>87000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>11300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-60600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>151400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>257300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>426400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>401800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>212600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>281600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>105100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>64000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>172300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>109400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>213500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>180400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>394400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>81700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>298400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1249500</v>
+        <v>1486700</v>
       </c>
       <c r="E21" s="3">
-        <v>1160600</v>
+        <v>1268300</v>
       </c>
       <c r="F21" s="3">
-        <v>1173400</v>
+        <v>1178100</v>
       </c>
       <c r="G21" s="3">
-        <v>1409400</v>
+        <v>1191100</v>
       </c>
       <c r="H21" s="3">
-        <v>1100000</v>
+        <v>1435800</v>
       </c>
       <c r="I21" s="3">
-        <v>1113800</v>
+        <v>1116600</v>
       </c>
       <c r="J21" s="3">
+        <v>1130600</v>
+      </c>
+      <c r="K21" s="3">
         <v>1804400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1225900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1465700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1335800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1121400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1144900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1126200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1233300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1255100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1783600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1888900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1584500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1712100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1406800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1694300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1652200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1376200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1600300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1668200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1822700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1389400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1580800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1445600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1976,192 +2015,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>631300</v>
+        <v>846100</v>
       </c>
       <c r="E23" s="3">
-        <v>593600</v>
+        <v>640800</v>
       </c>
       <c r="F23" s="3">
-        <v>555700</v>
+        <v>602500</v>
       </c>
       <c r="G23" s="3">
-        <v>791000</v>
+        <v>564100</v>
       </c>
       <c r="H23" s="3">
-        <v>534900</v>
+        <v>808100</v>
       </c>
       <c r="I23" s="3">
-        <v>568100</v>
+        <v>543000</v>
       </c>
       <c r="J23" s="3">
+        <v>576700</v>
+      </c>
+      <c r="K23" s="3">
         <v>1249600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>658800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>870500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>735400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>552900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>552700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>518400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>576900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>547100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1109900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1192600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>905600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>966400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>700700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1021800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1008600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>678100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>975200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1057700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1225900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>806000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>894100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>189900</v>
+        <v>259900</v>
       </c>
       <c r="E24" s="3">
-        <v>167600</v>
+        <v>192700</v>
       </c>
       <c r="F24" s="3">
-        <v>137300</v>
+        <v>170100</v>
       </c>
       <c r="G24" s="3">
-        <v>186400</v>
+        <v>139400</v>
       </c>
       <c r="H24" s="3">
-        <v>124600</v>
+        <v>194500</v>
       </c>
       <c r="I24" s="3">
-        <v>140900</v>
+        <v>126500</v>
       </c>
       <c r="J24" s="3">
+        <v>143000</v>
+      </c>
+      <c r="K24" s="3">
         <v>574000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>226000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>278400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>216500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>179500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>187500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>167500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>146500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>86600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>325100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>349300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>265200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>120600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-77300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>310300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>281100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>135400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>142100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>348400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>403800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>300000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>336300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>295100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2252,192 +2300,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>441400</v>
+        <v>586300</v>
       </c>
       <c r="E26" s="3">
-        <v>426000</v>
+        <v>448100</v>
       </c>
       <c r="F26" s="3">
-        <v>418400</v>
+        <v>432400</v>
       </c>
       <c r="G26" s="3">
-        <v>604600</v>
+        <v>424700</v>
       </c>
       <c r="H26" s="3">
-        <v>410300</v>
+        <v>613700</v>
       </c>
       <c r="I26" s="3">
-        <v>427300</v>
+        <v>416500</v>
       </c>
       <c r="J26" s="3">
+        <v>433700</v>
+      </c>
+      <c r="K26" s="3">
         <v>675600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>432900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>592100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>518900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>373300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>365200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>350800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>430400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>460500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>784800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>843300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>640300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>845800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>777900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>711500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>727500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>542700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>833100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>709300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>822100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>506000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>682500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>599000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>432500</v>
+        <v>614000</v>
       </c>
       <c r="E27" s="3">
-        <v>418100</v>
+        <v>439000</v>
       </c>
       <c r="F27" s="3">
-        <v>409600</v>
+        <v>424400</v>
       </c>
       <c r="G27" s="3">
-        <v>595000</v>
+        <v>415800</v>
       </c>
       <c r="H27" s="3">
-        <v>401000</v>
+        <v>604000</v>
       </c>
       <c r="I27" s="3">
-        <v>411200</v>
+        <v>407000</v>
       </c>
       <c r="J27" s="3">
+        <v>417400</v>
+      </c>
+      <c r="K27" s="3">
         <v>668300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>444200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>587400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>479300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>365300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>353100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>341200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>426900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>455800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>775900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>826500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>634000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>841200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>766100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>697700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>726700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>513000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>817400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>689400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>811000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>497800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>665000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2528,8 +2585,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2551,11 +2611,11 @@
       <c r="I29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J29" s="3">
+      <c r="J29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K29" s="3">
         <v>900</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -2563,11 +2623,11 @@
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3">
         <v>-8200</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
@@ -2575,11 +2635,11 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
         <v>58500</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2593,14 +2653,14 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2611,8 +2671,8 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
@@ -2620,8 +2680,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2712,8 +2775,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2804,192 +2870,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-94900</v>
+        <v>-198000</v>
       </c>
       <c r="E32" s="3">
-        <v>-40800</v>
+        <v>-96300</v>
       </c>
       <c r="F32" s="3">
-        <v>-45500</v>
+        <v>-41400</v>
       </c>
       <c r="G32" s="3">
-        <v>-198800</v>
+        <v>-46200</v>
       </c>
       <c r="H32" s="3">
-        <v>-89600</v>
+        <v>-201800</v>
       </c>
       <c r="I32" s="3">
-        <v>-11400</v>
+        <v>-90900</v>
       </c>
       <c r="J32" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1117000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-155900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-99500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>14100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-87000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-11300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>60600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-151400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-257300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-426400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-401800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-212600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-281600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-105100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-64000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-172300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-109400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-213500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-180400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-394400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-81700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-298400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-194000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>432500</v>
+        <v>614000</v>
       </c>
       <c r="E33" s="3">
-        <v>418100</v>
+        <v>439000</v>
       </c>
       <c r="F33" s="3">
-        <v>409600</v>
+        <v>424400</v>
       </c>
       <c r="G33" s="3">
-        <v>595000</v>
+        <v>415800</v>
       </c>
       <c r="H33" s="3">
-        <v>401000</v>
+        <v>604000</v>
       </c>
       <c r="I33" s="3">
-        <v>411200</v>
+        <v>407000</v>
       </c>
       <c r="J33" s="3">
+        <v>417400</v>
+      </c>
+      <c r="K33" s="3">
         <v>669300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>444200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>587400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>479300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>357100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>353100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>341200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>426900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>514300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>775900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>826500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>634000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>841200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>766100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>697700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>726700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>513000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>817400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>689400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>811000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>497800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>665000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3080,197 +3155,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>432500</v>
+        <v>614000</v>
       </c>
       <c r="E35" s="3">
-        <v>418100</v>
+        <v>439000</v>
       </c>
       <c r="F35" s="3">
-        <v>409600</v>
+        <v>424400</v>
       </c>
       <c r="G35" s="3">
-        <v>595000</v>
+        <v>415800</v>
       </c>
       <c r="H35" s="3">
-        <v>401000</v>
+        <v>604000</v>
       </c>
       <c r="I35" s="3">
-        <v>411200</v>
+        <v>407000</v>
       </c>
       <c r="J35" s="3">
+        <v>417400</v>
+      </c>
+      <c r="K35" s="3">
         <v>669300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>444200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>587400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>479300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>357100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>353100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>341200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>426900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>514300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>775900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>826500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>634000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>841200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>766100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>697700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>726700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>513000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>817400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>689400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>811000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>497800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>665000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3303,8 +3387,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3337,100 +3422,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7000100</v>
+        <v>7043900</v>
       </c>
       <c r="E41" s="3">
-        <v>7041500</v>
+        <v>7105500</v>
       </c>
       <c r="F41" s="3">
-        <v>9076300</v>
+        <v>7147500</v>
       </c>
       <c r="G41" s="3">
-        <v>7085000</v>
+        <v>9213000</v>
       </c>
       <c r="H41" s="3">
-        <v>6945600</v>
+        <v>7191700</v>
       </c>
       <c r="I41" s="3">
-        <v>6606700</v>
+        <v>7050200</v>
       </c>
       <c r="J41" s="3">
+        <v>6706200</v>
+      </c>
+      <c r="K41" s="3">
         <v>7249600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7084100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8377200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8349700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7654200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8305200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10183900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10067500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10001900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9297700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10195800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10468300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12335200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12604300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11656800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12061800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12702300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11964900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11518800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11731700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10051600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>9284500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>9275800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3521,192 +3610,201 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2023400</v>
+        <v>2112900</v>
       </c>
       <c r="E43" s="3">
-        <v>2399900</v>
+        <v>2053900</v>
       </c>
       <c r="F43" s="3">
-        <v>2503800</v>
+        <v>2436000</v>
       </c>
       <c r="G43" s="3">
-        <v>1997700</v>
+        <v>2541500</v>
       </c>
       <c r="H43" s="3">
-        <v>1925100</v>
+        <v>2027700</v>
       </c>
       <c r="I43" s="3">
-        <v>2217800</v>
+        <v>1954100</v>
       </c>
       <c r="J43" s="3">
+        <v>2251200</v>
+      </c>
+      <c r="K43" s="3">
         <v>1928900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1578100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1519400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1779900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1952500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1566800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1312300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1704500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2254500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1999500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1879200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2136800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2139000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1930100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2040800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2255700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2170500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2281800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1973500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1850500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1988700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1868400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1833400</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1480100</v>
+        <v>1558200</v>
       </c>
       <c r="E44" s="3">
-        <v>1128900</v>
+        <v>1502400</v>
       </c>
       <c r="F44" s="3">
-        <v>1122300</v>
+        <v>1145900</v>
       </c>
       <c r="G44" s="3">
-        <v>968800</v>
+        <v>1139200</v>
       </c>
       <c r="H44" s="3">
-        <v>1026300</v>
+        <v>983400</v>
       </c>
       <c r="I44" s="3">
-        <v>972500</v>
+        <v>1041800</v>
       </c>
       <c r="J44" s="3">
+        <v>987100</v>
+      </c>
+      <c r="K44" s="3">
         <v>926700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>948200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>958100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1006200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1007900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1080000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1053500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1105000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1110200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1202100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1161000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1146700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1111800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1369000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1220500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1117200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1003400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1246700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1174100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1116500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1045400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1265400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1328700</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3797,8 +3895,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3889,215 +3990,224 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>54739600</v>
+        <v>55717400</v>
       </c>
       <c r="E47" s="3">
-        <v>54257600</v>
+        <v>55563900</v>
       </c>
       <c r="F47" s="3">
-        <v>51919200</v>
+        <v>55074700</v>
       </c>
       <c r="G47" s="3">
-        <v>51446600</v>
+        <v>52701200</v>
       </c>
       <c r="H47" s="3">
-        <v>53107300</v>
+        <v>52221400</v>
       </c>
       <c r="I47" s="3">
-        <v>52637800</v>
+        <v>53907100</v>
       </c>
       <c r="J47" s="3">
+        <v>53430500</v>
+      </c>
+      <c r="K47" s="3">
         <v>51081400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>52315800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>52503500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>52973200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>51182600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>51463300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>53541500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>58386100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>59973800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>74441200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>71989200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>69844300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>82078400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>78817700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>75266400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>69855700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>69467000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>71014900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>70684000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>70420000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>69927900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>70281800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>67221000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17337500</v>
+        <v>17752700</v>
       </c>
       <c r="E48" s="3">
-        <v>16863100</v>
+        <v>17598600</v>
       </c>
       <c r="F48" s="3">
-        <v>16014500</v>
+        <v>17117000</v>
       </c>
       <c r="G48" s="3">
-        <v>15161700</v>
+        <v>16255700</v>
       </c>
       <c r="H48" s="3">
-        <v>15122700</v>
+        <v>15390000</v>
       </c>
       <c r="I48" s="3">
-        <v>15142200</v>
+        <v>15350500</v>
       </c>
       <c r="J48" s="3">
+        <v>15370200</v>
+      </c>
+      <c r="K48" s="3">
         <v>15042700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15489200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16390700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15748800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15218300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16071400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16625000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18395500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19086100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6587600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6033700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6371700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5285700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5647800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5234600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5009900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4951600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4682600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4655100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4632500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4521200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4311900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4267300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>8002600</v>
+        <v>7972000</v>
       </c>
       <c r="E49" s="3">
-        <v>7608300</v>
+        <v>8123200</v>
       </c>
       <c r="F49" s="3">
-        <v>7934100</v>
+        <v>7722900</v>
       </c>
       <c r="G49" s="3">
-        <v>6203900</v>
+        <v>8053600</v>
       </c>
       <c r="H49" s="3">
-        <v>6352300</v>
+        <v>6297300</v>
       </c>
       <c r="I49" s="3">
-        <v>5926000</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>8</v>
+        <v>6448000</v>
+      </c>
+      <c r="J49" s="3">
+        <v>6015300</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>8</v>
@@ -4111,8 +4221,8 @@
       <c r="N49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -4165,8 +4275,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4257,8 +4370,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4349,8 +4465,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4441,8 +4560,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4533,100 +4655,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>104880300</v>
+        <v>106284300</v>
       </c>
       <c r="E54" s="3">
-        <v>103478700</v>
+        <v>106459800</v>
       </c>
       <c r="F54" s="3">
-        <v>101521500</v>
+        <v>105037100</v>
       </c>
       <c r="G54" s="3">
-        <v>96637800</v>
+        <v>103050500</v>
       </c>
       <c r="H54" s="3">
-        <v>98179100</v>
+        <v>98093200</v>
       </c>
       <c r="I54" s="3">
-        <v>97093300</v>
+        <v>99657700</v>
       </c>
       <c r="J54" s="3">
+        <v>98555600</v>
+      </c>
+      <c r="K54" s="3">
         <v>94757300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>96806300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>99748000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>99827500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>96162300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>97668500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>102579300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>111679100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>115124900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>116999300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>114976800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>113629300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>117001000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>114429700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>109422700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>103370600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>103290900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>104429300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>103291400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>102314200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>99626900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>98834300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>95642500</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4659,8 +4787,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4693,284 +4822,294 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2190200</v>
+        <v>2227900</v>
       </c>
       <c r="E57" s="3">
-        <v>2091500</v>
+        <v>2223100</v>
       </c>
       <c r="F57" s="3">
-        <v>2435900</v>
+        <v>2123000</v>
       </c>
       <c r="G57" s="3">
-        <v>1678400</v>
+        <v>2472600</v>
       </c>
       <c r="H57" s="3">
-        <v>1650200</v>
+        <v>1703600</v>
       </c>
       <c r="I57" s="3">
-        <v>1748200</v>
+        <v>1675000</v>
       </c>
       <c r="J57" s="3">
+        <v>1774500</v>
+      </c>
+      <c r="K57" s="3">
         <v>1935000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1556000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1660300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1546400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1848400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1558500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1535100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1627400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2490800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2067100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2140100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2032100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2820300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2206000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2131700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2416200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2371200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1898700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1915700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1891500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2233500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1846800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1846700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3893600</v>
+        <v>4360100</v>
       </c>
       <c r="E58" s="3">
-        <v>3820400</v>
+        <v>3952200</v>
       </c>
       <c r="F58" s="3">
-        <v>5503400</v>
+        <v>3877900</v>
       </c>
       <c r="G58" s="3">
-        <v>2958400</v>
+        <v>5586300</v>
       </c>
       <c r="H58" s="3">
-        <v>3065500</v>
+        <v>3002900</v>
       </c>
       <c r="I58" s="3">
-        <v>3925400</v>
+        <v>3111700</v>
       </c>
       <c r="J58" s="3">
+        <v>3984500</v>
+      </c>
+      <c r="K58" s="3">
         <v>2919200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4574600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3561600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3355000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2178500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2722800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2816300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3217100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2967500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3499400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2525500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3084300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2974800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6124400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3014300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2165000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2773100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3241500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3034400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3398100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2514400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2628100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1852200</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>18004600</v>
+        <v>18450500</v>
       </c>
       <c r="E59" s="3">
-        <v>18085800</v>
+        <v>18275800</v>
       </c>
       <c r="F59" s="3">
-        <v>22175000</v>
+        <v>18358200</v>
       </c>
       <c r="G59" s="3">
-        <v>17535200</v>
+        <v>22508900</v>
       </c>
       <c r="H59" s="3">
-        <v>17051200</v>
+        <v>17799300</v>
       </c>
       <c r="I59" s="3">
-        <v>17313700</v>
+        <v>17308000</v>
       </c>
       <c r="J59" s="3">
+        <v>17574500</v>
+      </c>
+      <c r="K59" s="3">
         <v>20002500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18559000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19455100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19718700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21080400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19858200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20846200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22491300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22800700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>23138900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>22619100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>21575000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>21945200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>21264700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21021000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>19682100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>19204700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>19329900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>19044800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>18495000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>18275000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17244500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>16647500</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5061,100 +5200,106 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>36176300</v>
+        <v>35949200</v>
       </c>
       <c r="E61" s="3">
-        <v>35031700</v>
+        <v>36721200</v>
       </c>
       <c r="F61" s="3">
-        <v>34592600</v>
+        <v>35559300</v>
       </c>
       <c r="G61" s="3">
-        <v>31604500</v>
+        <v>35113500</v>
       </c>
       <c r="H61" s="3">
-        <v>32859400</v>
+        <v>32080500</v>
       </c>
       <c r="I61" s="3">
-        <v>31313900</v>
+        <v>33354300</v>
       </c>
       <c r="J61" s="3">
+        <v>31785500</v>
+      </c>
+      <c r="K61" s="3">
         <v>29446700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>29889600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31374300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>31744800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>31339600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>31786500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>33212400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>37004500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>37701100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>37525700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>37410700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>37668500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>40229600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>37481900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>35869000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>34202200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>34591600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>35174700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>34962700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>35088200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>34193700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>34384900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>33751200</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5245,8 +5390,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5337,8 +5485,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5429,8 +5580,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5521,100 +5675,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>79906600</v>
+        <v>81161600</v>
       </c>
       <c r="E66" s="3">
-        <v>79287200</v>
+        <v>81110000</v>
       </c>
       <c r="F66" s="3">
-        <v>77992000</v>
+        <v>80481300</v>
       </c>
       <c r="G66" s="3">
-        <v>75021900</v>
+        <v>79166500</v>
       </c>
       <c r="H66" s="3">
-        <v>75969500</v>
+        <v>76151700</v>
       </c>
       <c r="I66" s="3">
-        <v>75223000</v>
+        <v>77113600</v>
       </c>
       <c r="J66" s="3">
+        <v>76355800</v>
+      </c>
+      <c r="K66" s="3">
         <v>73101400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>75179800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>77269700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>77428100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>74690500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>76131100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>79367500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>86642100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>88751200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>89592700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>87755300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>87183700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>89160100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>87832500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>83373800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>78716600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>79041800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>80311500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>79690300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>79485200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>77383600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>77218100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>74665300</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5647,8 +5807,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5739,8 +5900,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5831,8 +5995,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5923,8 +6090,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6015,100 +6185,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>20798700</v>
+        <v>21391100</v>
       </c>
       <c r="E72" s="3">
-        <v>20366200</v>
+        <v>21112000</v>
       </c>
       <c r="F72" s="3">
-        <v>20281500</v>
+        <v>20673000</v>
       </c>
       <c r="G72" s="3">
-        <v>20015700</v>
+        <v>20587000</v>
       </c>
       <c r="H72" s="3">
-        <v>19756600</v>
+        <v>20317200</v>
       </c>
       <c r="I72" s="3">
-        <v>19358800</v>
+        <v>20054100</v>
       </c>
       <c r="J72" s="3">
+        <v>19650300</v>
+      </c>
+      <c r="K72" s="3">
         <v>19317900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19625900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20469500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20268200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19459100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20219500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>21453300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>23117700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>24266800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>24561300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>24406600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>23503000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>24559200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>23318000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>22550800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>21382600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>20930200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>20440400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19935700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19246400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>18427200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>17917900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>17520500</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6199,8 +6375,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6291,8 +6470,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6383,100 +6565,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>24973700</v>
+        <v>25122700</v>
       </c>
       <c r="E76" s="3">
-        <v>24191600</v>
+        <v>25349800</v>
       </c>
       <c r="F76" s="3">
-        <v>23529600</v>
+        <v>24555900</v>
       </c>
       <c r="G76" s="3">
-        <v>21615900</v>
+        <v>23883900</v>
       </c>
       <c r="H76" s="3">
-        <v>22209600</v>
+        <v>21941500</v>
       </c>
       <c r="I76" s="3">
-        <v>21870300</v>
+        <v>22544000</v>
       </c>
       <c r="J76" s="3">
+        <v>22199700</v>
+      </c>
+      <c r="K76" s="3">
         <v>21655800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21626500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22478300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22399400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21471800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21537500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23211700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>25037000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26373700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>27406600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>27221500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>26445600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>27840900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>26597200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>26048900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>24653900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>24249100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24117900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23601100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>22829000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>22243300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>21616300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20977200</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6567,197 +6755,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>432500</v>
+        <v>614000</v>
       </c>
       <c r="E81" s="3">
-        <v>418100</v>
+        <v>439000</v>
       </c>
       <c r="F81" s="3">
-        <v>409600</v>
+        <v>424400</v>
       </c>
       <c r="G81" s="3">
-        <v>595000</v>
+        <v>415800</v>
       </c>
       <c r="H81" s="3">
-        <v>401000</v>
+        <v>604000</v>
       </c>
       <c r="I81" s="3">
-        <v>411200</v>
+        <v>407000</v>
       </c>
       <c r="J81" s="3">
+        <v>417400</v>
+      </c>
+      <c r="K81" s="3">
         <v>669300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>444200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>587400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>479300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>357100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>353100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>341200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>426900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>514300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>775900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>826500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>634000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>841200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>766100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>697700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>726700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>513000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>817400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>689400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>811000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>497800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>665000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6790,100 +6987,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>618200</v>
+        <v>640500</v>
       </c>
       <c r="E83" s="3">
-        <v>567000</v>
+        <v>627500</v>
       </c>
       <c r="F83" s="3">
-        <v>617700</v>
+        <v>575600</v>
       </c>
       <c r="G83" s="3">
-        <v>618400</v>
+        <v>627000</v>
       </c>
       <c r="H83" s="3">
-        <v>565100</v>
+        <v>627700</v>
       </c>
       <c r="I83" s="3">
-        <v>545700</v>
+        <v>573600</v>
       </c>
       <c r="J83" s="3">
+        <v>553900</v>
+      </c>
+      <c r="K83" s="3">
         <v>554900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>567100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>595200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>600400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>568500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>592200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>607800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>656400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>708000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>673700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>696300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>678900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>745700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>706100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>672500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>643600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>698100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>625100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>610500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>596800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>583400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>562000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>551500</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6974,8 +7175,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7066,8 +7270,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7158,8 +7365,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7250,8 +7460,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7342,100 +7555,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2617000</v>
+        <v>2261600</v>
       </c>
       <c r="E89" s="3">
-        <v>1307400</v>
+        <v>2656400</v>
       </c>
       <c r="F89" s="3">
-        <v>2214200</v>
+        <v>1327100</v>
       </c>
       <c r="G89" s="3">
-        <v>2103000</v>
+        <v>2247500</v>
       </c>
       <c r="H89" s="3">
-        <v>1956500</v>
+        <v>2134700</v>
       </c>
       <c r="I89" s="3">
-        <v>-210800</v>
+        <v>1985900</v>
       </c>
       <c r="J89" s="3">
+        <v>-214000</v>
+      </c>
+      <c r="K89" s="3">
         <v>2243300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1184200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2698700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1608600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2407900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1732000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2631100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1552600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2834900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1711200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3255200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1636300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1980300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1020200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1637600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>884100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1772000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1193700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1172300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>803500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1250000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>994000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1888000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7468,100 +7687,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-292529000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-336475000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-321237000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-303186000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-298865000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-254596000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-223427000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-248094000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-229768000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-256101000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-39500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-42700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-84600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-133300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-79200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-172200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-116600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-62600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-48600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-106500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-127700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-198600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-147500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-155900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-197500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-222200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2642900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2149200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2170900</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7652,8 +7875,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7744,100 +7970,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2989500</v>
+        <v>-2395300</v>
       </c>
       <c r="E94" s="3">
-        <v>-2720100</v>
+        <v>-3034500</v>
       </c>
       <c r="F94" s="3">
-        <v>-2700900</v>
+        <v>-2761100</v>
       </c>
       <c r="G94" s="3">
-        <v>-1667700</v>
+        <v>-2741600</v>
       </c>
       <c r="H94" s="3">
-        <v>-1418300</v>
+        <v>-1692800</v>
       </c>
       <c r="I94" s="3">
-        <v>-1507000</v>
+        <v>-1439700</v>
       </c>
       <c r="J94" s="3">
+        <v>-1529700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-236300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2314500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2310200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-852200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2514400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3140600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1425100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2023400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3372700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3499800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3389900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3065100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1698000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3863100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2709000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>32500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-760600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1359900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>116900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1077700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1208800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-357200</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7870,100 +8102,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-334900</v>
       </c>
       <c r="E96" s="3">
-        <v>-333400</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-338400</v>
       </c>
       <c r="G96" s="3">
-        <v>-335900</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-340900</v>
       </c>
       <c r="I96" s="3">
-        <v>-369900</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-375400</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-322600</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-385400</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-320100</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-439200</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-408700</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-540100</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-363000</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-454400</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-312700</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-345000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-267500</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8054,8 +8290,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8146,8 +8385,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8238,280 +8480,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>284400</v>
+        <v>121700</v>
       </c>
       <c r="E100" s="3">
-        <v>-753600</v>
+        <v>288700</v>
       </c>
       <c r="F100" s="3">
-        <v>2450400</v>
+        <v>-764900</v>
       </c>
       <c r="G100" s="3">
-        <v>-177800</v>
+        <v>2487300</v>
       </c>
       <c r="H100" s="3">
-        <v>-282300</v>
+        <v>-180500</v>
       </c>
       <c r="I100" s="3">
-        <v>920000</v>
+        <v>-286500</v>
       </c>
       <c r="J100" s="3">
+        <v>933800</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1715900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>192400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-205900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-350200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-356000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>131600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-216700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>852700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1587500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>927700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-136900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>197600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-769700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3671900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>352000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1637300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-330300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>571200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>434300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>622800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>713600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-108100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-426900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>46700</v>
+        <v>-49700</v>
       </c>
       <c r="E101" s="3">
-        <v>131500</v>
+        <v>47400</v>
       </c>
       <c r="F101" s="3">
-        <v>27500</v>
+        <v>133400</v>
       </c>
       <c r="G101" s="3">
-        <v>-118200</v>
+        <v>27900</v>
       </c>
       <c r="H101" s="3">
-        <v>83000</v>
+        <v>-119900</v>
       </c>
       <c r="I101" s="3">
-        <v>154900</v>
+        <v>84200</v>
       </c>
       <c r="J101" s="3">
+        <v>157300</v>
+      </c>
+      <c r="K101" s="3">
         <v>111600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>39900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>83400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-39400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>51700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-35300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-58100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-8700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-69800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>49100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>10000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-82800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>24000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>42100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>41400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>141000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-42500</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-41400</v>
+        <v>-61600</v>
       </c>
       <c r="E102" s="3">
-        <v>-2034800</v>
+        <v>-42000</v>
       </c>
       <c r="F102" s="3">
-        <v>1991300</v>
+        <v>-2065400</v>
       </c>
       <c r="G102" s="3">
-        <v>139400</v>
+        <v>2021300</v>
       </c>
       <c r="H102" s="3">
-        <v>338800</v>
+        <v>141500</v>
       </c>
       <c r="I102" s="3">
-        <v>-642900</v>
+        <v>343900</v>
       </c>
       <c r="J102" s="3">
+        <v>-652600</v>
+      </c>
+      <c r="K102" s="3">
         <v>402700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-898100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>186600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>414800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-379100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1277400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>989800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>383500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1010300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-809300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-306900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1289300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-496100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>759200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-670400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-710700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>798800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>424100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-166800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1487500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>874100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-181900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1061400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>IX</t>
   </si>
@@ -656,413 +656,425 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4570600</v>
+        <v>4954100</v>
       </c>
       <c r="E8" s="3">
-        <v>4601800</v>
+        <v>4326400</v>
       </c>
       <c r="F8" s="3">
-        <v>4562800</v>
+        <v>4356000</v>
       </c>
       <c r="G8" s="3">
-        <v>4526100</v>
+        <v>4319100</v>
       </c>
       <c r="H8" s="3">
-        <v>4246400</v>
+        <v>4267000</v>
       </c>
       <c r="I8" s="3">
-        <v>4765200</v>
+        <v>4019600</v>
       </c>
       <c r="J8" s="3">
+        <v>4510700</v>
+      </c>
+      <c r="K8" s="3">
         <v>4433700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4331000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4304600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4561900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4474800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4445500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4258400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4261900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4586100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5250300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5208200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5394500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5023800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6138000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5042300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6113700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5489600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6037700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6120900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6558500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7162400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6678100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6250200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5616300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2519900</v>
+        <v>2899900</v>
       </c>
       <c r="E9" s="3">
-        <v>2653300</v>
+        <v>2385300</v>
       </c>
       <c r="F9" s="3">
-        <v>2677800</v>
+        <v>2511600</v>
       </c>
       <c r="G9" s="3">
-        <v>2735900</v>
+        <v>2534800</v>
       </c>
       <c r="H9" s="3">
-        <v>2332300</v>
+        <v>2446500</v>
       </c>
       <c r="I9" s="3">
-        <v>3152100</v>
+        <v>2207700</v>
       </c>
       <c r="J9" s="3">
+        <v>2983700</v>
+      </c>
+      <c r="K9" s="3">
         <v>2816500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2792900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2639600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2863300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2678900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2911600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2651900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2623600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2965900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3323400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3188900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3275300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2984300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3960200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3109200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3952000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3459500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4148400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4173600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4727200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5316600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4878500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4517300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3914700</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2050700</v>
+        <v>2054200</v>
       </c>
       <c r="E10" s="3">
-        <v>1948500</v>
+        <v>1941200</v>
       </c>
       <c r="F10" s="3">
-        <v>1885000</v>
+        <v>1844400</v>
       </c>
       <c r="G10" s="3">
-        <v>1790200</v>
+        <v>1784300</v>
       </c>
       <c r="H10" s="3">
-        <v>1914100</v>
+        <v>1820600</v>
       </c>
       <c r="I10" s="3">
-        <v>1613100</v>
+        <v>1811900</v>
       </c>
       <c r="J10" s="3">
+        <v>1527000</v>
+      </c>
+      <c r="K10" s="3">
         <v>1617200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1538100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1665000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1698700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1795800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1534000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1606500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1638300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1620200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1926900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2019300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2119200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2039500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2177800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1933100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2161700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2030100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1889300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1947200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1831300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1845700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1799600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1732900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1701600</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1096,8 +1108,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1191,8 +1204,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1286,198 +1302,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E14" s="3">
         <v>700</v>
       </c>
-      <c r="E14" s="3">
-        <v>3000</v>
-      </c>
       <c r="F14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G14" s="3">
+        <v>500</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J14" s="3">
+        <v>900</v>
+      </c>
+      <c r="K14" s="3">
+        <v>700</v>
+      </c>
+      <c r="L14" s="3">
+        <v>136800</v>
+      </c>
+      <c r="M14" s="3">
+        <v>102900</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H14" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>700</v>
-      </c>
-      <c r="K14" s="3">
-        <v>136800</v>
-      </c>
-      <c r="L14" s="3">
-        <v>102900</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>600</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-35000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>22500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>23000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>22600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>14100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>9800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>38400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>30100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>15800</v>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E15" s="3">
-        <v>15300</v>
+        <v>14900</v>
       </c>
       <c r="F15" s="3">
-        <v>14300</v>
+        <v>14500</v>
       </c>
       <c r="G15" s="3">
-        <v>12200</v>
+        <v>13600</v>
       </c>
       <c r="H15" s="3">
-        <v>14900</v>
+        <v>11500</v>
       </c>
       <c r="I15" s="3">
-        <v>14700</v>
+        <v>14100</v>
       </c>
       <c r="J15" s="3">
+        <v>13900</v>
+      </c>
+      <c r="K15" s="3">
         <v>14600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>15400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>17500</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>15100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>16500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>16700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>20100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>17200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>16400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>16200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>13200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>12500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>10500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>9900</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD15" s="3">
         <v>11400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>11000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>13300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>11900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1508,198 +1533,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3922400</v>
+        <v>4312800</v>
       </c>
       <c r="E17" s="3">
-        <v>4057300</v>
+        <v>3712900</v>
       </c>
       <c r="F17" s="3">
-        <v>4001700</v>
+        <v>3840600</v>
       </c>
       <c r="G17" s="3">
-        <v>4008200</v>
+        <v>3787900</v>
       </c>
       <c r="H17" s="3">
-        <v>3640000</v>
+        <v>3653200</v>
       </c>
       <c r="I17" s="3">
-        <v>4313200</v>
+        <v>3445600</v>
       </c>
       <c r="J17" s="3">
+        <v>4082800</v>
+      </c>
+      <c r="K17" s="3">
         <v>3868600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4198400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3801700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3790900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3725200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3979600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3717000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3682900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4160600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4960500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4524800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4603700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4330800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5453200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4446700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5155900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4653400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5469000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5359200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5681200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6330900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5953800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5529800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4916200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>648100</v>
+        <v>641300</v>
       </c>
       <c r="E18" s="3">
-        <v>544500</v>
+        <v>613500</v>
       </c>
       <c r="F18" s="3">
-        <v>561100</v>
+        <v>515400</v>
       </c>
       <c r="G18" s="3">
-        <v>517900</v>
+        <v>531100</v>
       </c>
       <c r="H18" s="3">
-        <v>606400</v>
+        <v>613900</v>
       </c>
       <c r="I18" s="3">
-        <v>452000</v>
+        <v>574000</v>
       </c>
       <c r="J18" s="3">
+        <v>427900</v>
+      </c>
+      <c r="K18" s="3">
         <v>565100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>132600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>502900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>771000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>749500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>465900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>541400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>579000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>425500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>289800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>683400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>790800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>693000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>684800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>595600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>957800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>836200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>568700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>761700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>877300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>831500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>724300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>720400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>700100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1733,198 +1765,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>198000</v>
+        <v>379300</v>
       </c>
       <c r="E20" s="3">
-        <v>96300</v>
+        <v>187400</v>
       </c>
       <c r="F20" s="3">
-        <v>41400</v>
+        <v>91200</v>
       </c>
       <c r="G20" s="3">
-        <v>46200</v>
+        <v>39200</v>
       </c>
       <c r="H20" s="3">
-        <v>201800</v>
+        <v>63400</v>
       </c>
       <c r="I20" s="3">
-        <v>90900</v>
+        <v>191000</v>
       </c>
       <c r="J20" s="3">
+        <v>86100</v>
+      </c>
+      <c r="K20" s="3">
         <v>11600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1117000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>155900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>99500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-14100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>87000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>11300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-60600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>151400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>257300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>426400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>401800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>212600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>281600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>105100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>64000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>172300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>109400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>213500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>180400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>394400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>81700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>298400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1486700</v>
+        <v>1599300</v>
       </c>
       <c r="E21" s="3">
-        <v>1268300</v>
+        <v>1407300</v>
       </c>
       <c r="F21" s="3">
-        <v>1178100</v>
+        <v>1200600</v>
       </c>
       <c r="G21" s="3">
-        <v>1191100</v>
+        <v>1115100</v>
       </c>
       <c r="H21" s="3">
-        <v>1435800</v>
+        <v>1270700</v>
       </c>
       <c r="I21" s="3">
-        <v>1116600</v>
+        <v>1359100</v>
       </c>
       <c r="J21" s="3">
+        <v>1056900</v>
+      </c>
+      <c r="K21" s="3">
         <v>1130600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1804400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1225900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1465700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1335800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1121400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1144900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1126200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1233300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1255100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1783600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1888900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1584500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1712100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1406800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1694300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1652200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1376200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1600300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1668200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1822700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1389400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1580800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1445600</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2018,198 +2057,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>846100</v>
+        <v>1020600</v>
       </c>
       <c r="E23" s="3">
-        <v>640800</v>
+        <v>800900</v>
       </c>
       <c r="F23" s="3">
-        <v>602500</v>
+        <v>606600</v>
       </c>
       <c r="G23" s="3">
-        <v>564100</v>
+        <v>570300</v>
       </c>
       <c r="H23" s="3">
-        <v>808100</v>
+        <v>677200</v>
       </c>
       <c r="I23" s="3">
-        <v>543000</v>
+        <v>765000</v>
       </c>
       <c r="J23" s="3">
+        <v>514000</v>
+      </c>
+      <c r="K23" s="3">
         <v>576700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1249600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>658800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>870500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>735400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>552900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>552700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>518400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>576900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>547100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1109900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1192600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>905600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>966400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>700700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1021800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1008600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>678100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>975200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1057700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1225900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>806000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>894100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>259900</v>
+        <v>248900</v>
       </c>
       <c r="E24" s="3">
-        <v>192700</v>
+        <v>246000</v>
       </c>
       <c r="F24" s="3">
-        <v>170100</v>
+        <v>182400</v>
       </c>
       <c r="G24" s="3">
-        <v>139400</v>
+        <v>161000</v>
       </c>
       <c r="H24" s="3">
-        <v>194500</v>
+        <v>168500</v>
       </c>
       <c r="I24" s="3">
-        <v>126500</v>
+        <v>184100</v>
       </c>
       <c r="J24" s="3">
+        <v>119700</v>
+      </c>
+      <c r="K24" s="3">
         <v>143000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>574000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>226000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>278400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>216500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>179500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>187500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>167500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>146500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>86600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>325100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>349300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>265200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>120600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-77300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>310300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>281100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>135400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>142100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>348400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>403800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>300000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>336300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>295100</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2303,198 +2351,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>586300</v>
+        <v>771700</v>
       </c>
       <c r="E26" s="3">
-        <v>448100</v>
+        <v>555000</v>
       </c>
       <c r="F26" s="3">
-        <v>432400</v>
+        <v>424200</v>
       </c>
       <c r="G26" s="3">
-        <v>424700</v>
+        <v>409300</v>
       </c>
       <c r="H26" s="3">
-        <v>613700</v>
+        <v>508800</v>
       </c>
       <c r="I26" s="3">
-        <v>416500</v>
+        <v>580900</v>
       </c>
       <c r="J26" s="3">
+        <v>394200</v>
+      </c>
+      <c r="K26" s="3">
         <v>433700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>675600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>432900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>592100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>518900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>373300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>365200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>350800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>430400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>460500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>784800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>843300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>640300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>845800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>777900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>711500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>727500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>542700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>833100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>709300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>822100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>506000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>682500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>599000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>614000</v>
+        <v>809800</v>
       </c>
       <c r="E27" s="3">
-        <v>439000</v>
+        <v>581200</v>
       </c>
       <c r="F27" s="3">
-        <v>424400</v>
+        <v>415600</v>
       </c>
       <c r="G27" s="3">
-        <v>415800</v>
+        <v>401700</v>
       </c>
       <c r="H27" s="3">
-        <v>604000</v>
+        <v>500300</v>
       </c>
       <c r="I27" s="3">
-        <v>407000</v>
+        <v>571700</v>
       </c>
       <c r="J27" s="3">
+        <v>385300</v>
+      </c>
+      <c r="K27" s="3">
         <v>417400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>668300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>444200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>587400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>479300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>365300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>353100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>341200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>426900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>455800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>775900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>826500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>634000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>841200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>766100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>697700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>726700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>513000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>817400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>689400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>811000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>497800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>665000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2588,8 +2645,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2614,11 +2674,11 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="3">
         <v>900</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -2626,11 +2686,11 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3">
         <v>-8200</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
@@ -2638,11 +2698,11 @@
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3">
         <v>58500</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2656,14 +2716,14 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2674,8 +2734,8 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
@@ -2683,8 +2743,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2778,8 +2841,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2873,198 +2939,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-198000</v>
+        <v>-379300</v>
       </c>
       <c r="E32" s="3">
-        <v>-96300</v>
+        <v>-187400</v>
       </c>
       <c r="F32" s="3">
-        <v>-41400</v>
+        <v>-91200</v>
       </c>
       <c r="G32" s="3">
-        <v>-46200</v>
+        <v>-39200</v>
       </c>
       <c r="H32" s="3">
-        <v>-201800</v>
+        <v>-63400</v>
       </c>
       <c r="I32" s="3">
-        <v>-90900</v>
+        <v>-191000</v>
       </c>
       <c r="J32" s="3">
+        <v>-86100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-11600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1117000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-155900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-99500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>14100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-87000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>60600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-151400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-257300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-426400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-401800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-212600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-281600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-105100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-64000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-172300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-109400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-213500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-180400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-394400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-81700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-298400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-194000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>614000</v>
+        <v>809800</v>
       </c>
       <c r="E33" s="3">
-        <v>439000</v>
+        <v>581200</v>
       </c>
       <c r="F33" s="3">
-        <v>424400</v>
+        <v>415600</v>
       </c>
       <c r="G33" s="3">
-        <v>415800</v>
+        <v>401700</v>
       </c>
       <c r="H33" s="3">
-        <v>604000</v>
+        <v>500300</v>
       </c>
       <c r="I33" s="3">
-        <v>407000</v>
+        <v>571700</v>
       </c>
       <c r="J33" s="3">
+        <v>385300</v>
+      </c>
+      <c r="K33" s="3">
         <v>417400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>669300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>444200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>587400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>479300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>357100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>353100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>341200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>426900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>514300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>775900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>826500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>634000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>841200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>766100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>697700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>726700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>513000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>817400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>689400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>811000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>497800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>665000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3158,203 +3233,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>614000</v>
+        <v>809800</v>
       </c>
       <c r="E35" s="3">
-        <v>439000</v>
+        <v>581200</v>
       </c>
       <c r="F35" s="3">
-        <v>424400</v>
+        <v>415600</v>
       </c>
       <c r="G35" s="3">
-        <v>415800</v>
+        <v>401700</v>
       </c>
       <c r="H35" s="3">
-        <v>604000</v>
+        <v>500300</v>
       </c>
       <c r="I35" s="3">
-        <v>407000</v>
+        <v>571700</v>
       </c>
       <c r="J35" s="3">
+        <v>385300</v>
+      </c>
+      <c r="K35" s="3">
         <v>417400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>669300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>444200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>587400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>479300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>357100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>353100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>341200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>426900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>514300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>775900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>826500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>634000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>841200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>766100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>697700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>726700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>513000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>817400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>689400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>811000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>497800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>665000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3388,8 +3472,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3423,103 +3508,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7043900</v>
+        <v>7562300</v>
       </c>
       <c r="E41" s="3">
-        <v>7105500</v>
+        <v>6667700</v>
       </c>
       <c r="F41" s="3">
-        <v>7147500</v>
+        <v>6726000</v>
       </c>
       <c r="G41" s="3">
-        <v>9213000</v>
+        <v>6765800</v>
       </c>
       <c r="H41" s="3">
-        <v>7191700</v>
+        <v>8720900</v>
       </c>
       <c r="I41" s="3">
-        <v>7050200</v>
+        <v>6807600</v>
       </c>
       <c r="J41" s="3">
+        <v>6673600</v>
+      </c>
+      <c r="K41" s="3">
         <v>6706200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7249600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7084100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8377200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8349700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7654200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8305200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10183900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10067500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10001900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9297700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10195800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10468300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12335200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12604300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11656800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12061800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>12702300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11964900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11518800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11731700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10051600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>9284500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>9275800</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3613,198 +3702,207 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2112900</v>
+        <v>2190000</v>
       </c>
       <c r="E43" s="3">
-        <v>2053900</v>
+        <v>2000100</v>
       </c>
       <c r="F43" s="3">
-        <v>2436000</v>
+        <v>1944200</v>
       </c>
       <c r="G43" s="3">
-        <v>2541500</v>
+        <v>2305900</v>
       </c>
       <c r="H43" s="3">
-        <v>2027700</v>
+        <v>2405800</v>
       </c>
       <c r="I43" s="3">
-        <v>1954100</v>
+        <v>1919400</v>
       </c>
       <c r="J43" s="3">
+        <v>1849700</v>
+      </c>
+      <c r="K43" s="3">
         <v>2251200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1928900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1578100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1519400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1779900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1952500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1566800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1312300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1704500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2254500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1999500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1879200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2136800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2139000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1930100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2040800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2255700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2170500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2281800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1973500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1850500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1988700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1868400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1833400</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1558200</v>
+        <v>1450600</v>
       </c>
       <c r="E44" s="3">
-        <v>1502400</v>
+        <v>1475000</v>
       </c>
       <c r="F44" s="3">
-        <v>1145900</v>
+        <v>1422100</v>
       </c>
       <c r="G44" s="3">
-        <v>1139200</v>
+        <v>1084700</v>
       </c>
       <c r="H44" s="3">
-        <v>983400</v>
+        <v>1078400</v>
       </c>
       <c r="I44" s="3">
-        <v>1041800</v>
+        <v>930900</v>
       </c>
       <c r="J44" s="3">
+        <v>986100</v>
+      </c>
+      <c r="K44" s="3">
         <v>987100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>926700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>948200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>958100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1006200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1007900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1080000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1053500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1105000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1110200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1202100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1161000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1146700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1111800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1369000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1220500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1117200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1003400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1246700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1174100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1116500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1045400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1265400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1328700</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3898,8 +3996,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3993,224 +4094,233 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>55717400</v>
+        <v>54458300</v>
       </c>
       <c r="E47" s="3">
-        <v>55563900</v>
+        <v>52741400</v>
       </c>
       <c r="F47" s="3">
-        <v>55074700</v>
+        <v>52596100</v>
       </c>
       <c r="G47" s="3">
-        <v>52701200</v>
+        <v>52133000</v>
       </c>
       <c r="H47" s="3">
-        <v>52221400</v>
+        <v>49886300</v>
       </c>
       <c r="I47" s="3">
-        <v>53907100</v>
+        <v>49432100</v>
       </c>
       <c r="J47" s="3">
+        <v>51027800</v>
+      </c>
+      <c r="K47" s="3">
         <v>53430500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>51081400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>52315800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>52503500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>52973200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>51182600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>51463300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>53541500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>58386100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>59973800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>74441200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>71989200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>69844300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>82078400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>78817700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>75266400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>69855700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>69467000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>71014900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>70684000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>70420000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>69927900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>70281800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>67221000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17752700</v>
+        <v>17906100</v>
       </c>
       <c r="E48" s="3">
-        <v>17598600</v>
+        <v>16804500</v>
       </c>
       <c r="F48" s="3">
-        <v>17117000</v>
+        <v>16658600</v>
       </c>
       <c r="G48" s="3">
-        <v>16255700</v>
+        <v>16202800</v>
       </c>
       <c r="H48" s="3">
-        <v>15390000</v>
+        <v>15387400</v>
       </c>
       <c r="I48" s="3">
-        <v>15350500</v>
+        <v>14568000</v>
       </c>
       <c r="J48" s="3">
+        <v>14530600</v>
+      </c>
+      <c r="K48" s="3">
         <v>15370200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15042700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15489200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16390700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15748800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15218300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16071400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16625000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>18395500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19086100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6587600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6033700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6371700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5285700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5647800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5234600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5009900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4951600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4682600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4655100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4632500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4521200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4311900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4267300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>7972000</v>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E49" s="3">
-        <v>8123200</v>
+        <v>7546200</v>
       </c>
       <c r="F49" s="3">
-        <v>7722900</v>
+        <v>7689300</v>
       </c>
       <c r="G49" s="3">
-        <v>8053600</v>
+        <v>7310400</v>
       </c>
       <c r="H49" s="3">
-        <v>6297300</v>
+        <v>7623400</v>
       </c>
       <c r="I49" s="3">
-        <v>6448000</v>
+        <v>5960900</v>
       </c>
       <c r="J49" s="3">
+        <v>6103600</v>
+      </c>
+      <c r="K49" s="3">
         <v>6015300</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>8</v>
@@ -4224,8 +4334,8 @@
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -4278,8 +4388,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4373,8 +4486,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4468,8 +4584,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4563,8 +4682,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4658,103 +4780,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>106284300</v>
+        <v>104135000</v>
       </c>
       <c r="E54" s="3">
-        <v>106459800</v>
+        <v>100607400</v>
       </c>
       <c r="F54" s="3">
-        <v>105037100</v>
+        <v>100773500</v>
       </c>
       <c r="G54" s="3">
-        <v>103050500</v>
+        <v>99426800</v>
       </c>
       <c r="H54" s="3">
-        <v>98093200</v>
+        <v>97546300</v>
       </c>
       <c r="I54" s="3">
-        <v>99657700</v>
+        <v>92853800</v>
       </c>
       <c r="J54" s="3">
+        <v>94334700</v>
+      </c>
+      <c r="K54" s="3">
         <v>98555600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>94757300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>96806300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>99748000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>99827500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>96162300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>97668500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>102579300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>111679100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>115124900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>116999300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>114976800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>113629300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>117001000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>114429700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>109422700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>103370600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>103290900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>104429300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>103291400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>102314200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>99626900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>98834300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>95642500</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4788,8 +4916,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4823,293 +4952,303 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2227900</v>
+        <v>2312800</v>
       </c>
       <c r="E57" s="3">
-        <v>2223100</v>
+        <v>2108900</v>
       </c>
       <c r="F57" s="3">
-        <v>2123000</v>
+        <v>2104400</v>
       </c>
       <c r="G57" s="3">
-        <v>2472600</v>
+        <v>2009600</v>
       </c>
       <c r="H57" s="3">
-        <v>1703600</v>
+        <v>2340500</v>
       </c>
       <c r="I57" s="3">
-        <v>1675000</v>
+        <v>1612600</v>
       </c>
       <c r="J57" s="3">
+        <v>1585600</v>
+      </c>
+      <c r="K57" s="3">
         <v>1774500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1935000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1556000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1660300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1546400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1848400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1558500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1535100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1627400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2490800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2067100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2140100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2032100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2820300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2206000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2131700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2416200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2371200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1898700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1915700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1891500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2233500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1846800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1846700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4360100</v>
+        <v>3662700</v>
       </c>
       <c r="E58" s="3">
-        <v>3952200</v>
+        <v>4127200</v>
       </c>
       <c r="F58" s="3">
-        <v>3877900</v>
+        <v>3741100</v>
       </c>
       <c r="G58" s="3">
-        <v>5586300</v>
+        <v>3670800</v>
       </c>
       <c r="H58" s="3">
-        <v>3002900</v>
+        <v>5287900</v>
       </c>
       <c r="I58" s="3">
-        <v>3111700</v>
+        <v>2842500</v>
       </c>
       <c r="J58" s="3">
+        <v>2945500</v>
+      </c>
+      <c r="K58" s="3">
         <v>3984500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2919200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4574600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3561600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3355000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2178500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2722800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2816300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3217100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2967500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3499400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2525500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3084300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2974800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6124400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3014300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2165000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2773100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3241500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3034400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3398100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2514400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2628100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1852200</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>18450500</v>
+        <v>17969600</v>
       </c>
       <c r="E59" s="3">
-        <v>18275800</v>
+        <v>17465000</v>
       </c>
       <c r="F59" s="3">
-        <v>18358200</v>
+        <v>17299600</v>
       </c>
       <c r="G59" s="3">
-        <v>22508900</v>
+        <v>17377600</v>
       </c>
       <c r="H59" s="3">
-        <v>17799300</v>
+        <v>21306700</v>
       </c>
       <c r="I59" s="3">
-        <v>17308000</v>
+        <v>16848600</v>
       </c>
       <c r="J59" s="3">
+        <v>16383500</v>
+      </c>
+      <c r="K59" s="3">
         <v>17574500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20002500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18559000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19455100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19718700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21080400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19858200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20846200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22491300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22800700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>23138900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>22619100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>21575000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>21945200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21264700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21021000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>19682100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>19204700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>19329900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>19044800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>18495000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>18275000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>17244500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>16647500</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5203,103 +5342,109 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>35949200</v>
+        <v>35896300</v>
       </c>
       <c r="E61" s="3">
-        <v>36721200</v>
+        <v>34029100</v>
       </c>
       <c r="F61" s="3">
-        <v>35559300</v>
+        <v>34759800</v>
       </c>
       <c r="G61" s="3">
-        <v>35113500</v>
+        <v>33660000</v>
       </c>
       <c r="H61" s="3">
-        <v>32080500</v>
+        <v>33238000</v>
       </c>
       <c r="I61" s="3">
-        <v>33354300</v>
+        <v>30367000</v>
       </c>
       <c r="J61" s="3">
+        <v>31572800</v>
+      </c>
+      <c r="K61" s="3">
         <v>31785500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>29446700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>29889600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>31374300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>31744800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>31339600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>31786500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>33212400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>37004500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>37701100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>37525700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>37410700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>37668500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>40229600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>37481900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>35869000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>34202200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>34591600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>35174700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>34962700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>35088200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>34193700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>34384900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>33751200</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5393,8 +5538,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5488,8 +5636,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5583,8 +5734,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5678,103 +5832,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>81161600</v>
+        <v>78988400</v>
       </c>
       <c r="E66" s="3">
-        <v>81110000</v>
+        <v>76826600</v>
       </c>
       <c r="F66" s="3">
-        <v>80481300</v>
+        <v>76777700</v>
       </c>
       <c r="G66" s="3">
-        <v>79166500</v>
+        <v>76182600</v>
       </c>
       <c r="H66" s="3">
-        <v>76151700</v>
+        <v>74938100</v>
       </c>
       <c r="I66" s="3">
-        <v>77113600</v>
+        <v>72084300</v>
       </c>
       <c r="J66" s="3">
+        <v>72994800</v>
+      </c>
+      <c r="K66" s="3">
         <v>76355800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73101400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>75179800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>77269700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>77428100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>74690500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>76131100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>79367500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>86642100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>88751200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>89592700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>87755300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>87183700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>89160100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>87832500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>83373800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>78716600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>79041800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>80311500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>79690300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>79485200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>77383600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>77218100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>74665300</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5808,8 +5968,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5903,8 +6064,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5998,8 +6162,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6093,8 +6260,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6188,103 +6358,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>21391100</v>
+        <v>20797100</v>
       </c>
       <c r="E72" s="3">
-        <v>21112000</v>
+        <v>20248600</v>
       </c>
       <c r="F72" s="3">
-        <v>20673000</v>
+        <v>19984300</v>
       </c>
       <c r="G72" s="3">
-        <v>20587000</v>
+        <v>19568800</v>
       </c>
       <c r="H72" s="3">
-        <v>20317200</v>
+        <v>19487400</v>
       </c>
       <c r="I72" s="3">
-        <v>20054100</v>
+        <v>19232000</v>
       </c>
       <c r="J72" s="3">
+        <v>18983000</v>
+      </c>
+      <c r="K72" s="3">
         <v>19650300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19317900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19625900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20469500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20268200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19459100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20219500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>21453300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>23117700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>24266800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>24561300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>24406600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>23503000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>24559200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>23318000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>22550800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>21382600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>20930200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>20440400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19935700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19246400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>18427200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>17917900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>17520500</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6378,8 +6554,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6473,8 +6652,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6568,103 +6750,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>25122700</v>
+        <v>25146600</v>
       </c>
       <c r="E76" s="3">
-        <v>25349800</v>
+        <v>23780800</v>
       </c>
       <c r="F76" s="3">
-        <v>24555900</v>
+        <v>23995800</v>
       </c>
       <c r="G76" s="3">
-        <v>23883900</v>
+        <v>23244300</v>
       </c>
       <c r="H76" s="3">
-        <v>21941500</v>
+        <v>22608200</v>
       </c>
       <c r="I76" s="3">
-        <v>22544000</v>
+        <v>20769500</v>
       </c>
       <c r="J76" s="3">
+        <v>21339900</v>
+      </c>
+      <c r="K76" s="3">
         <v>22199700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21655800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21626500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22478300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22399400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21471800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21537500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23211700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>25037000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26373700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>27406600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>27221500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>26445600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>27840900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>26597200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>26048900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>24653900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24249100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>24117900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>23601100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>22829000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>22243300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>21616300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20977200</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6758,203 +6946,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>614000</v>
+        <v>809800</v>
       </c>
       <c r="E81" s="3">
-        <v>439000</v>
+        <v>581200</v>
       </c>
       <c r="F81" s="3">
-        <v>424400</v>
+        <v>415600</v>
       </c>
       <c r="G81" s="3">
-        <v>415800</v>
+        <v>401700</v>
       </c>
       <c r="H81" s="3">
-        <v>604000</v>
+        <v>500300</v>
       </c>
       <c r="I81" s="3">
-        <v>407000</v>
+        <v>571700</v>
       </c>
       <c r="J81" s="3">
+        <v>385300</v>
+      </c>
+      <c r="K81" s="3">
         <v>417400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>669300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>444200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>587400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>479300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>357100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>353100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>341200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>426900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>514300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>775900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>826500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>634000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>841200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>766100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>697700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>726700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>513000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>817400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>689400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>811000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>497800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>665000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6988,103 +7185,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>640500</v>
+        <v>578700</v>
       </c>
       <c r="E83" s="3">
-        <v>627500</v>
+        <v>606300</v>
       </c>
       <c r="F83" s="3">
-        <v>575600</v>
+        <v>594000</v>
       </c>
       <c r="G83" s="3">
-        <v>627000</v>
+        <v>544800</v>
       </c>
       <c r="H83" s="3">
-        <v>627700</v>
+        <v>593500</v>
       </c>
       <c r="I83" s="3">
-        <v>573600</v>
+        <v>594200</v>
       </c>
       <c r="J83" s="3">
+        <v>543000</v>
+      </c>
+      <c r="K83" s="3">
         <v>553900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>554900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>567100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>595200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>600400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>568500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>592200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>607800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>656400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>708000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>673700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>696300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>678900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>745700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>706100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>672500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>643600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>698100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>625100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>610500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>596800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>583400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>562000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>551500</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7178,8 +7379,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7273,8 +7477,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7368,8 +7575,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7463,8 +7673,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7558,103 +7771,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2261600</v>
+        <v>2021300</v>
       </c>
       <c r="E89" s="3">
-        <v>2656400</v>
+        <v>2140800</v>
       </c>
       <c r="F89" s="3">
-        <v>1327100</v>
+        <v>2514500</v>
       </c>
       <c r="G89" s="3">
-        <v>2247500</v>
+        <v>1256200</v>
       </c>
       <c r="H89" s="3">
-        <v>2134700</v>
+        <v>2127500</v>
       </c>
       <c r="I89" s="3">
-        <v>1985900</v>
+        <v>2020700</v>
       </c>
       <c r="J89" s="3">
+        <v>1879900</v>
+      </c>
+      <c r="K89" s="3">
         <v>-214000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2243300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1184200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2698700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1608600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2407900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1732000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2631100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1552600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2834900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1711200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3255200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1636300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1980300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1020200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1637600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>884100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1772000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1193700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1172300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>803500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1250000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>994000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1888000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7688,103 +7907,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-250633000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-292529000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-336475000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-321237000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-303186000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-298865000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-254596000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-223427000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-248094000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-229768000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-256101000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-39500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-42700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-84600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-133300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-79200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-172200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-116600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-62600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-48600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-106500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-127700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-198600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-147500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-155900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-197500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-222200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2642900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2149200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2170900</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7878,8 +8101,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7973,103 +8199,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2395300</v>
+        <v>-1005100</v>
       </c>
       <c r="E94" s="3">
-        <v>-3034500</v>
+        <v>-2267300</v>
       </c>
       <c r="F94" s="3">
-        <v>-2761100</v>
+        <v>-2872400</v>
       </c>
       <c r="G94" s="3">
-        <v>-2741600</v>
+        <v>-2613600</v>
       </c>
       <c r="H94" s="3">
-        <v>-1692800</v>
+        <v>-2595100</v>
       </c>
       <c r="I94" s="3">
-        <v>-1439700</v>
+        <v>-1602400</v>
       </c>
       <c r="J94" s="3">
+        <v>-1362800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1529700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-236300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2314500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2310200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-852200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2514400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3140600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1425100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2023400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3372700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3499800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3389900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3065100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1698000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3863100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2709000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>32500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-760600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1359900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>116900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1077700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1208800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-357200</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8103,103 +8335,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-334900</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-317000</v>
       </c>
       <c r="F96" s="3">
-        <v>-338400</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-320300</v>
       </c>
       <c r="H96" s="3">
-        <v>-340900</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-322700</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-375400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-322600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-385400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-320100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-439200</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-408700</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-540100</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-363000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-454400</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-312700</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-345000</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-267500</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8293,8 +8529,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8388,8 +8627,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8483,289 +8725,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>121700</v>
+        <v>-209700</v>
       </c>
       <c r="E100" s="3">
-        <v>288700</v>
+        <v>115200</v>
       </c>
       <c r="F100" s="3">
-        <v>-764900</v>
+        <v>273200</v>
       </c>
       <c r="G100" s="3">
-        <v>2487300</v>
+        <v>-724100</v>
       </c>
       <c r="H100" s="3">
-        <v>-180500</v>
+        <v>2354500</v>
       </c>
       <c r="I100" s="3">
-        <v>-286500</v>
+        <v>-170800</v>
       </c>
       <c r="J100" s="3">
+        <v>-271200</v>
+      </c>
+      <c r="K100" s="3">
         <v>933800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1715900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>192400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-205900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-350200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-356000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>131600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-216700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>852700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1587500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>927700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-136900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>197600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-769700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3671900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>352000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1637300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-330300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>571200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>434300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>622800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>713600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-108100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-426900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-49700</v>
+        <v>88100</v>
       </c>
       <c r="E101" s="3">
-        <v>47400</v>
+        <v>-47000</v>
       </c>
       <c r="F101" s="3">
-        <v>133400</v>
+        <v>44800</v>
       </c>
       <c r="G101" s="3">
-        <v>27900</v>
+        <v>126300</v>
       </c>
       <c r="H101" s="3">
-        <v>-119900</v>
+        <v>26400</v>
       </c>
       <c r="I101" s="3">
-        <v>84200</v>
+        <v>-113500</v>
       </c>
       <c r="J101" s="3">
+        <v>79700</v>
+      </c>
+      <c r="K101" s="3">
         <v>157300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>111600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>39900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>8600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>83400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-39400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>51700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-35300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-58100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-8700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-69800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>49100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>10000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-82800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>24000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>42100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>41400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>141000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-42500</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-61600</v>
+        <v>894600</v>
       </c>
       <c r="E102" s="3">
-        <v>-42000</v>
+        <v>-58300</v>
       </c>
       <c r="F102" s="3">
-        <v>-2065400</v>
+        <v>-39800</v>
       </c>
       <c r="G102" s="3">
-        <v>2021300</v>
+        <v>-1955100</v>
       </c>
       <c r="H102" s="3">
-        <v>141500</v>
+        <v>1913300</v>
       </c>
       <c r="I102" s="3">
-        <v>343900</v>
+        <v>134000</v>
       </c>
       <c r="J102" s="3">
+        <v>325600</v>
+      </c>
+      <c r="K102" s="3">
         <v>-652600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>402700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-898100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>186600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>414800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-379100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1277400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>989800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>383500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1010300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-809300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-306900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1289300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-496100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>759200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-670400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-710700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>798800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>424100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-166800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1487500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>874100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-181900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1061400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>IX</t>
   </si>
@@ -656,425 +656,437 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4954100</v>
+        <v>5027800</v>
       </c>
       <c r="E8" s="3">
-        <v>4326400</v>
+        <v>5513200</v>
       </c>
       <c r="F8" s="3">
-        <v>4356000</v>
+        <v>4814700</v>
       </c>
       <c r="G8" s="3">
-        <v>4319100</v>
+        <v>4847600</v>
       </c>
       <c r="H8" s="3">
-        <v>4267000</v>
+        <v>4805300</v>
       </c>
       <c r="I8" s="3">
-        <v>4019600</v>
+        <v>4748600</v>
       </c>
       <c r="J8" s="3">
+        <v>4473200</v>
+      </c>
+      <c r="K8" s="3">
         <v>4510700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4433700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4331000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4304600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4561900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4474800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4445500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4258400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4261900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4586100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5250300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5208200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5394500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5023800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6138000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5042300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6113700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5489600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6037700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6120900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6558500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7162400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6678100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6250200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5616300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2899900</v>
+        <v>2933200</v>
       </c>
       <c r="E9" s="3">
-        <v>2385300</v>
+        <v>3227100</v>
       </c>
       <c r="F9" s="3">
-        <v>2511600</v>
+        <v>2654400</v>
       </c>
       <c r="G9" s="3">
-        <v>2534800</v>
+        <v>2795000</v>
       </c>
       <c r="H9" s="3">
-        <v>2446500</v>
+        <v>2820800</v>
       </c>
       <c r="I9" s="3">
-        <v>2207700</v>
+        <v>2722600</v>
       </c>
       <c r="J9" s="3">
+        <v>2456800</v>
+      </c>
+      <c r="K9" s="3">
         <v>2983700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2816500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2792900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2639600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2863300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2678900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2911600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2651900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2623600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2965900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3323400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3188900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3275300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2984300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3960200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3109200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3952000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3459500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4148400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4173600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4727200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5316600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4878500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4517300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3914700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2054200</v>
+        <v>2094600</v>
       </c>
       <c r="E10" s="3">
-        <v>1941200</v>
+        <v>2286000</v>
       </c>
       <c r="F10" s="3">
-        <v>1844400</v>
+        <v>2160200</v>
       </c>
       <c r="G10" s="3">
-        <v>1784300</v>
+        <v>2052600</v>
       </c>
       <c r="H10" s="3">
-        <v>1820600</v>
+        <v>1984400</v>
       </c>
       <c r="I10" s="3">
-        <v>1811900</v>
+        <v>2026000</v>
       </c>
       <c r="J10" s="3">
+        <v>2016400</v>
+      </c>
+      <c r="K10" s="3">
         <v>1527000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1617200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1538100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1665000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1698700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1795800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1534000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1606500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1638300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1620200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1926900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2019300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2119200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2039500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2177800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1933100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2161700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2030100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1889300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1947200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1831300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1845700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1799600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1732900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1701600</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1109,8 +1121,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1220,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1305,106 +1321,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>6900</v>
+        <v>600</v>
       </c>
       <c r="E14" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3">
-        <v>2900</v>
-      </c>
       <c r="G14" s="3">
-        <v>500</v>
+        <v>3200</v>
       </c>
       <c r="H14" s="3">
-        <v>2100</v>
+        <v>600</v>
       </c>
       <c r="I14" s="3">
-        <v>3400</v>
+        <v>2400</v>
       </c>
       <c r="J14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>136800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>102900</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>13000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-35000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>22500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>4700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>23000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>22600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>14100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>3500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>9800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>38400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>30100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1412,97 +1434,100 @@
         <v>8</v>
       </c>
       <c r="E15" s="3">
-        <v>14900</v>
+        <v>17900</v>
       </c>
       <c r="F15" s="3">
-        <v>14500</v>
+        <v>16600</v>
       </c>
       <c r="G15" s="3">
-        <v>13600</v>
+        <v>16100</v>
       </c>
       <c r="H15" s="3">
-        <v>11500</v>
+        <v>15100</v>
       </c>
       <c r="I15" s="3">
-        <v>14100</v>
+        <v>12900</v>
       </c>
       <c r="J15" s="3">
+        <v>15700</v>
+      </c>
+      <c r="K15" s="3">
         <v>13900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>15400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>14800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>17500</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>15100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>16500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>16700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>20100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>17200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>16400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>16200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>13200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>12500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>10500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>9900</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE15" s="3">
         <v>11400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>11000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>13300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>11900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1534,204 +1559,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4312800</v>
+        <v>4415300</v>
       </c>
       <c r="E17" s="3">
-        <v>3712900</v>
+        <v>4799500</v>
       </c>
       <c r="F17" s="3">
-        <v>3840600</v>
+        <v>4131900</v>
       </c>
       <c r="G17" s="3">
-        <v>3787900</v>
+        <v>4274000</v>
       </c>
       <c r="H17" s="3">
-        <v>3653200</v>
+        <v>4215900</v>
       </c>
       <c r="I17" s="3">
-        <v>3445600</v>
+        <v>4065400</v>
       </c>
       <c r="J17" s="3">
+        <v>3834400</v>
+      </c>
+      <c r="K17" s="3">
         <v>4082800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3868600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4198400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3801700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3790900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3725200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3979600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3717000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3682900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4160600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4960500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4524800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4603700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4330800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5453200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4446700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5155900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4653400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5469000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5359200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5681200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6330900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5953800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5529800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4916200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>641300</v>
+        <v>612500</v>
       </c>
       <c r="E18" s="3">
-        <v>613500</v>
+        <v>713700</v>
       </c>
       <c r="F18" s="3">
-        <v>515400</v>
+        <v>682800</v>
       </c>
       <c r="G18" s="3">
-        <v>531100</v>
+        <v>573600</v>
       </c>
       <c r="H18" s="3">
-        <v>613900</v>
+        <v>589300</v>
       </c>
       <c r="I18" s="3">
-        <v>574000</v>
+        <v>683100</v>
       </c>
       <c r="J18" s="3">
+        <v>638800</v>
+      </c>
+      <c r="K18" s="3">
         <v>427900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>565100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>132600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>502900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>771000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>749500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>465900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>541400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>579000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>425500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>289800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>683400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>790800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>693000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>684800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>595600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>957800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>836200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>568700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>761700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>877300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>831500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>724300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>720400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>700100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1766,204 +1798,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>379300</v>
+        <v>240700</v>
       </c>
       <c r="E20" s="3">
-        <v>187400</v>
+        <v>422100</v>
       </c>
       <c r="F20" s="3">
-        <v>91200</v>
+        <v>208600</v>
       </c>
       <c r="G20" s="3">
-        <v>39200</v>
+        <v>101500</v>
       </c>
       <c r="H20" s="3">
-        <v>63400</v>
+        <v>45400</v>
       </c>
       <c r="I20" s="3">
-        <v>191000</v>
+        <v>70500</v>
       </c>
       <c r="J20" s="3">
+        <v>212500</v>
+      </c>
+      <c r="K20" s="3">
         <v>86100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1117000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>155900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>99500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-14100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>87000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>11300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-60600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>151400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>257300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>426400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>401800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>212600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>281600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>105100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>64000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>172300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>109400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>213500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>180400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>394400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>81700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>298400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>1599300</v>
+      <c r="D21" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E21" s="3">
-        <v>1407300</v>
+        <v>1779800</v>
       </c>
       <c r="F21" s="3">
-        <v>1200600</v>
+        <v>1566100</v>
       </c>
       <c r="G21" s="3">
-        <v>1115100</v>
+        <v>1942400</v>
       </c>
       <c r="H21" s="3">
-        <v>1270700</v>
+        <v>-1268400</v>
       </c>
       <c r="I21" s="3">
-        <v>1359100</v>
+        <v>1414100</v>
       </c>
       <c r="J21" s="3">
+        <v>1512500</v>
+      </c>
+      <c r="K21" s="3">
         <v>1056900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1130600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1804400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1225900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1465700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1335800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1121400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1144900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1126200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1233300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1255100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1783600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1888900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1584500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1712100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1406800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1694300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1652200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1376200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1600300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1668200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1822700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1389400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1580800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1445600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2060,204 +2099,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1020600</v>
+        <v>853200</v>
       </c>
       <c r="E23" s="3">
-        <v>800900</v>
+        <v>1135800</v>
       </c>
       <c r="F23" s="3">
-        <v>606600</v>
+        <v>891300</v>
       </c>
       <c r="G23" s="3">
-        <v>570300</v>
+        <v>675000</v>
       </c>
       <c r="H23" s="3">
-        <v>677200</v>
+        <v>634700</v>
       </c>
       <c r="I23" s="3">
-        <v>765000</v>
+        <v>753700</v>
       </c>
       <c r="J23" s="3">
+        <v>851300</v>
+      </c>
+      <c r="K23" s="3">
         <v>514000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>576700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1249600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>658800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>870500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>735400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>552900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>552700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>518400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>576900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>547100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1109900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1192600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>905600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>966400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>700700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1021800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1008600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>678100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>975200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1057700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1225900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>806000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>894100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>248900</v>
+        <v>248500</v>
       </c>
       <c r="E24" s="3">
-        <v>246000</v>
+        <v>276900</v>
       </c>
       <c r="F24" s="3">
-        <v>182400</v>
+        <v>273700</v>
       </c>
       <c r="G24" s="3">
-        <v>161000</v>
+        <v>203000</v>
       </c>
       <c r="H24" s="3">
-        <v>168500</v>
+        <v>179200</v>
       </c>
       <c r="I24" s="3">
-        <v>184100</v>
+        <v>187500</v>
       </c>
       <c r="J24" s="3">
+        <v>204900</v>
+      </c>
+      <c r="K24" s="3">
         <v>119700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>143000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>574000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>226000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>278400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>216500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>179500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>187500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>167500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>146500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>86600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>325100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>349300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>265200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>120600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-77300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>310300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>281100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>135400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>142100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>348400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>403800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>300000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>336300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>295100</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2354,204 +2402,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>771700</v>
+        <v>604700</v>
       </c>
       <c r="E26" s="3">
-        <v>555000</v>
+        <v>858800</v>
       </c>
       <c r="F26" s="3">
-        <v>424200</v>
+        <v>617600</v>
       </c>
       <c r="G26" s="3">
-        <v>409300</v>
+        <v>472000</v>
       </c>
       <c r="H26" s="3">
-        <v>508800</v>
+        <v>455500</v>
       </c>
       <c r="I26" s="3">
-        <v>580900</v>
+        <v>566200</v>
       </c>
       <c r="J26" s="3">
+        <v>646400</v>
+      </c>
+      <c r="K26" s="3">
         <v>394200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>433700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>675600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>432900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>592100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>518900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>373300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>365200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>350800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>430400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>460500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>784800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>843300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>640300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>845800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>777900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>711500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>727500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>542700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>833100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>709300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>822100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>506000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>682500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>599000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>809800</v>
+        <v>615800</v>
       </c>
       <c r="E27" s="3">
-        <v>581200</v>
+        <v>901100</v>
       </c>
       <c r="F27" s="3">
-        <v>415600</v>
+        <v>646800</v>
       </c>
       <c r="G27" s="3">
-        <v>401700</v>
+        <v>462500</v>
       </c>
       <c r="H27" s="3">
-        <v>500300</v>
+        <v>447100</v>
       </c>
       <c r="I27" s="3">
-        <v>571700</v>
+        <v>556800</v>
       </c>
       <c r="J27" s="3">
+        <v>636200</v>
+      </c>
+      <c r="K27" s="3">
         <v>385300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>417400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>668300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>444200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>587400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>479300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>365300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>353100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>341200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>426900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>455800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>775900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>826500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>634000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>841200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>766100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>697700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>726700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>513000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>817400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>689400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>811000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>497800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>665000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2648,8 +2705,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2677,11 +2737,11 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="3">
         <v>900</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
@@ -2689,11 +2749,11 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-8200</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2701,11 +2761,11 @@
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3">
         <v>58500</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2719,14 +2779,14 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2737,8 +2797,8 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG29" s="3">
         <v>0</v>
@@ -2746,8 +2806,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2844,8 +2907,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2942,204 +3008,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-379300</v>
+        <v>-240700</v>
       </c>
       <c r="E32" s="3">
-        <v>-187400</v>
+        <v>-422100</v>
       </c>
       <c r="F32" s="3">
-        <v>-91200</v>
+        <v>-208600</v>
       </c>
       <c r="G32" s="3">
-        <v>-39200</v>
+        <v>-101500</v>
       </c>
       <c r="H32" s="3">
-        <v>-63400</v>
+        <v>-45400</v>
       </c>
       <c r="I32" s="3">
-        <v>-191000</v>
+        <v>-70500</v>
       </c>
       <c r="J32" s="3">
+        <v>-212500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-86100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1117000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-155900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-99500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>14100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-87000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-11300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>60600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-151400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-257300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-426400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-401800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-212600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-281600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-105100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-64000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-172300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-109400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-213500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-180400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-394400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-81700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-298400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-194000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>809800</v>
+        <v>615800</v>
       </c>
       <c r="E33" s="3">
-        <v>581200</v>
+        <v>901100</v>
       </c>
       <c r="F33" s="3">
-        <v>415600</v>
+        <v>646800</v>
       </c>
       <c r="G33" s="3">
-        <v>401700</v>
+        <v>462500</v>
       </c>
       <c r="H33" s="3">
-        <v>500300</v>
+        <v>447100</v>
       </c>
       <c r="I33" s="3">
-        <v>571700</v>
+        <v>556800</v>
       </c>
       <c r="J33" s="3">
+        <v>636200</v>
+      </c>
+      <c r="K33" s="3">
         <v>385300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>417400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>669300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>444200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>587400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>479300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>357100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>353100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>341200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>426900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>514300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>775900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>826500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>634000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>841200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>766100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>697700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>726700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>513000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>817400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>689400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>811000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>497800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>665000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3236,209 +3311,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>809800</v>
+        <v>615800</v>
       </c>
       <c r="E35" s="3">
-        <v>581200</v>
+        <v>901100</v>
       </c>
       <c r="F35" s="3">
-        <v>415600</v>
+        <v>646800</v>
       </c>
       <c r="G35" s="3">
-        <v>401700</v>
+        <v>462500</v>
       </c>
       <c r="H35" s="3">
-        <v>500300</v>
+        <v>447100</v>
       </c>
       <c r="I35" s="3">
-        <v>571700</v>
+        <v>556800</v>
       </c>
       <c r="J35" s="3">
+        <v>636200</v>
+      </c>
+      <c r="K35" s="3">
         <v>385300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>417400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>669300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>444200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>587400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>479300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>357100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>353100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>341200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>426900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>514300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>775900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>826500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>634000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>841200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>766100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>697700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>726700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>513000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>817400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>689400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>811000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>497800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>665000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3473,8 +3557,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3509,106 +3594,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7562300</v>
+        <v>8212500</v>
       </c>
       <c r="E41" s="3">
-        <v>6667700</v>
+        <v>8415700</v>
       </c>
       <c r="F41" s="3">
-        <v>6726000</v>
+        <v>7420200</v>
       </c>
       <c r="G41" s="3">
-        <v>6765800</v>
+        <v>7485000</v>
       </c>
       <c r="H41" s="3">
-        <v>8720900</v>
+        <v>7529300</v>
       </c>
       <c r="I41" s="3">
-        <v>6807600</v>
+        <v>9705000</v>
       </c>
       <c r="J41" s="3">
+        <v>7575800</v>
+      </c>
+      <c r="K41" s="3">
         <v>6673600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6706200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7249600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7084100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8377200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8349700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7654200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8305200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10183900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10067500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10001900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9297700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10195800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10468300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12335200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12604300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11656800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>12061800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12702300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11964900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11518800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11731700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10051600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>9284500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>9275800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3705,204 +3794,213 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2190000</v>
+        <v>2301500</v>
       </c>
       <c r="E43" s="3">
-        <v>2000100</v>
+        <v>2437100</v>
       </c>
       <c r="F43" s="3">
-        <v>1944200</v>
+        <v>2225800</v>
       </c>
       <c r="G43" s="3">
-        <v>2305900</v>
+        <v>2163600</v>
       </c>
       <c r="H43" s="3">
-        <v>2405800</v>
+        <v>2566100</v>
       </c>
       <c r="I43" s="3">
-        <v>1919400</v>
+        <v>2672700</v>
       </c>
       <c r="J43" s="3">
+        <v>2136000</v>
+      </c>
+      <c r="K43" s="3">
         <v>1849700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2251200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1928900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1578100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1519400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1779900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1952500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1566800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1312300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1704500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2254500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1999500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1879200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2136800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2139000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1930100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2040800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2255700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2170500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2281800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1973500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1850500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1988700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1868400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1833400</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1450600</v>
+        <v>1543600</v>
       </c>
       <c r="E44" s="3">
-        <v>1475000</v>
+        <v>1614200</v>
       </c>
       <c r="F44" s="3">
-        <v>1422100</v>
+        <v>1641400</v>
       </c>
       <c r="G44" s="3">
-        <v>1084700</v>
+        <v>1582600</v>
       </c>
       <c r="H44" s="3">
-        <v>1078400</v>
+        <v>1207100</v>
       </c>
       <c r="I44" s="3">
-        <v>930900</v>
+        <v>1200000</v>
       </c>
       <c r="J44" s="3">
+        <v>1036000</v>
+      </c>
+      <c r="K44" s="3">
         <v>986100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>987100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>926700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>948200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>958100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1006200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1007900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1080000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1053500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1105000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1110200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1202100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1161000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1146700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1111800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1369000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1220500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1117200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1003400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1246700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1174100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1116500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1045400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1265400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1328700</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3999,8 +4097,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4097,233 +4198,242 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>54458300</v>
+        <v>60544200</v>
       </c>
       <c r="E47" s="3">
-        <v>52741400</v>
+        <v>60604000</v>
       </c>
       <c r="F47" s="3">
-        <v>52596100</v>
+        <v>58693400</v>
       </c>
       <c r="G47" s="3">
-        <v>52133000</v>
+        <v>58531800</v>
       </c>
       <c r="H47" s="3">
-        <v>49886300</v>
+        <v>58016400</v>
       </c>
       <c r="I47" s="3">
-        <v>49432100</v>
+        <v>55710800</v>
       </c>
       <c r="J47" s="3">
+        <v>55010700</v>
+      </c>
+      <c r="K47" s="3">
         <v>51027800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>53430500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>51081400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>52315800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>52503500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>52973200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>51182600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>51463300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>53541500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>58386100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>59973800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>74441200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>71989200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>69844300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>82078400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>78817700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>75266400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>69855700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>69467000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>71014900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>70684000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>70420000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>69927900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>70281800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>67221000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17906100</v>
+        <v>21182600</v>
       </c>
       <c r="E48" s="3">
-        <v>16804500</v>
+        <v>19926900</v>
       </c>
       <c r="F48" s="3">
-        <v>16658600</v>
+        <v>18701000</v>
       </c>
       <c r="G48" s="3">
-        <v>16202800</v>
+        <v>18538600</v>
       </c>
       <c r="H48" s="3">
-        <v>15387400</v>
+        <v>18031300</v>
       </c>
       <c r="I48" s="3">
-        <v>14568000</v>
+        <v>23333900</v>
       </c>
       <c r="J48" s="3">
+        <v>16212000</v>
+      </c>
+      <c r="K48" s="3">
         <v>14530600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15370200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15042700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15489200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16390700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15748800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15218300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16071400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>16625000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>18395500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19086100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6587600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6033700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6371700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5285700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5647800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5234600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5009900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4951600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4682600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4655100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4632500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4521200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4311900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4267300</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E49" s="3">
-        <v>7546200</v>
+      <c r="E49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F49" s="3">
-        <v>7689300</v>
+        <v>8397800</v>
       </c>
       <c r="G49" s="3">
-        <v>7310400</v>
+        <v>8557000</v>
       </c>
       <c r="H49" s="3">
-        <v>7623400</v>
+        <v>8135400</v>
       </c>
       <c r="I49" s="3">
-        <v>5960900</v>
+        <v>8483800</v>
       </c>
       <c r="J49" s="3">
+        <v>6633600</v>
+      </c>
+      <c r="K49" s="3">
         <v>6103600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6015300</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>8</v>
@@ -4337,8 +4447,8 @@
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -4391,8 +4501,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4489,8 +4602,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4587,8 +4703,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4685,8 +4804,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4783,106 +4905,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>104135000</v>
+        <v>117166800</v>
       </c>
       <c r="E54" s="3">
-        <v>100607400</v>
+        <v>115886900</v>
       </c>
       <c r="F54" s="3">
-        <v>100773500</v>
+        <v>111961200</v>
       </c>
       <c r="G54" s="3">
-        <v>99426800</v>
+        <v>112146100</v>
       </c>
       <c r="H54" s="3">
-        <v>97546300</v>
+        <v>110647400</v>
       </c>
       <c r="I54" s="3">
-        <v>92853800</v>
+        <v>108554600</v>
       </c>
       <c r="J54" s="3">
+        <v>103332600</v>
+      </c>
+      <c r="K54" s="3">
         <v>94334700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>98555600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>94757300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>96806300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>99748000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>99827500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>96162300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>97668500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>102579300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>111679100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>115124900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>116999300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>114976800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>113629300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>117001000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>114429700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>109422700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>103370600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>103290900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>104429300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>103291400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>102314200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>99626900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>98834300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>95642500</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4917,8 +5045,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4953,302 +5082,312 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2312800</v>
+        <v>2294100</v>
       </c>
       <c r="E57" s="3">
-        <v>2108900</v>
+        <v>2573800</v>
       </c>
       <c r="F57" s="3">
-        <v>2104400</v>
+        <v>2346900</v>
       </c>
       <c r="G57" s="3">
-        <v>2009600</v>
+        <v>2341900</v>
       </c>
       <c r="H57" s="3">
-        <v>2340500</v>
+        <v>2236400</v>
       </c>
       <c r="I57" s="3">
-        <v>1612600</v>
+        <v>2604600</v>
       </c>
       <c r="J57" s="3">
+        <v>1794600</v>
+      </c>
+      <c r="K57" s="3">
         <v>1585600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1774500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1935000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1556000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1660300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1546400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1848400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1558500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1535100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1627400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2490800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2067100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2140100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2032100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2820300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2206000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2131700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2416200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2371200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1898700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1915700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1891500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2233500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1846800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1846700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3662700</v>
+        <v>4558700</v>
       </c>
       <c r="E58" s="3">
-        <v>4127200</v>
+        <v>4076100</v>
       </c>
       <c r="F58" s="3">
-        <v>3741100</v>
+        <v>4593000</v>
       </c>
       <c r="G58" s="3">
-        <v>3670800</v>
+        <v>4163300</v>
       </c>
       <c r="H58" s="3">
-        <v>5287900</v>
+        <v>4085000</v>
       </c>
       <c r="I58" s="3">
-        <v>2842500</v>
+        <v>3612500</v>
       </c>
       <c r="J58" s="3">
+        <v>3163300</v>
+      </c>
+      <c r="K58" s="3">
         <v>2945500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3984500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2919200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4574600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3561600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3355000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2178500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2722800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2816300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3217100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2967500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3499400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2525500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3084300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2974800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6124400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3014300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2165000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2773100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3241500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3034400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3398100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2514400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2628100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1852200</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17969600</v>
+        <v>19427400</v>
       </c>
       <c r="E59" s="3">
-        <v>17465000</v>
+        <v>21771800</v>
       </c>
       <c r="F59" s="3">
-        <v>17299600</v>
+        <v>19436000</v>
       </c>
       <c r="G59" s="3">
-        <v>17377600</v>
+        <v>19251900</v>
       </c>
       <c r="H59" s="3">
-        <v>21306700</v>
+        <v>19338700</v>
       </c>
       <c r="I59" s="3">
-        <v>16848600</v>
+        <v>23711200</v>
       </c>
       <c r="J59" s="3">
+        <v>18750000</v>
+      </c>
+      <c r="K59" s="3">
         <v>16383500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17574500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20002500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18559000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19455100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19718700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21080400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19858200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>20846200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22491300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>22800700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>23138900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>22619100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>21575000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21945200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21264700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>21021000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>19682100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>19204700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>19329900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>19044800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>18495000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>18275000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>17244500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>16647500</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5345,106 +5484,112 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>35896300</v>
+        <v>40779000</v>
       </c>
       <c r="E61" s="3">
-        <v>34029100</v>
+        <v>40003200</v>
       </c>
       <c r="F61" s="3">
-        <v>34759800</v>
+        <v>37869400</v>
       </c>
       <c r="G61" s="3">
-        <v>33660000</v>
+        <v>38682500</v>
       </c>
       <c r="H61" s="3">
-        <v>33238000</v>
+        <v>37458600</v>
       </c>
       <c r="I61" s="3">
-        <v>30367000</v>
+        <v>37039600</v>
       </c>
       <c r="J61" s="3">
+        <v>33794000</v>
+      </c>
+      <c r="K61" s="3">
         <v>31572800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31785500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>29446700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>29889600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>31374300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>31744800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>31339600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>31786500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>33212400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>37004500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>37701100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>37525700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>37410700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>37668500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>40229600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>37481900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>35869000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>34202200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>34591600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>35174700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>34962700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>35088200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>34193700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>34384900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>33751200</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5541,8 +5686,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5639,8 +5787,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5737,8 +5888,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5835,106 +5989,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>78988400</v>
+        <v>88243900</v>
       </c>
       <c r="E66" s="3">
-        <v>76826600</v>
+        <v>87902500</v>
       </c>
       <c r="F66" s="3">
-        <v>76777700</v>
+        <v>85496700</v>
       </c>
       <c r="G66" s="3">
-        <v>76182600</v>
+        <v>85442300</v>
       </c>
       <c r="H66" s="3">
-        <v>74938100</v>
+        <v>84780000</v>
       </c>
       <c r="I66" s="3">
-        <v>72084300</v>
+        <v>83395000</v>
       </c>
       <c r="J66" s="3">
+        <v>80219200</v>
+      </c>
+      <c r="K66" s="3">
         <v>72994800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>76355800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>73101400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>75179800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>77269700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>77428100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>74690500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>76131100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>79367500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>86642100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>88751200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>89592700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>87755300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>87183700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>89160100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>87832500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>83373800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>78716600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>79041800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>80311500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>79690300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>79485200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>77383600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>77218100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>74665300</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5969,8 +6129,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6067,8 +6228,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6165,8 +6329,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6263,8 +6430,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6361,106 +6531,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>20797100</v>
+        <v>23301500</v>
       </c>
       <c r="E72" s="3">
-        <v>20248600</v>
+        <v>23144100</v>
       </c>
       <c r="F72" s="3">
-        <v>19984300</v>
+        <v>22533700</v>
       </c>
       <c r="G72" s="3">
-        <v>19568800</v>
+        <v>22239600</v>
       </c>
       <c r="H72" s="3">
-        <v>19487400</v>
+        <v>21777200</v>
       </c>
       <c r="I72" s="3">
-        <v>19232000</v>
+        <v>21686600</v>
       </c>
       <c r="J72" s="3">
+        <v>21402300</v>
+      </c>
+      <c r="K72" s="3">
         <v>18983000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19650300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19317900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19625900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20469500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20268200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19459100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20219500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>21453300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>23117700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>24266800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>24561300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>24406600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>23503000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>24559200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>23318000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>22550800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>21382600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>20930200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>20440400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19935700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19246400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18427200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>17917900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>17520500</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6557,8 +6733,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6655,8 +6834,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6753,106 +6935,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>25146600</v>
+        <v>28922900</v>
       </c>
       <c r="E76" s="3">
-        <v>23780800</v>
+        <v>27984400</v>
       </c>
       <c r="F76" s="3">
-        <v>23995800</v>
+        <v>26464600</v>
       </c>
       <c r="G76" s="3">
-        <v>23244300</v>
+        <v>26703800</v>
       </c>
       <c r="H76" s="3">
-        <v>22608200</v>
+        <v>25867500</v>
       </c>
       <c r="I76" s="3">
-        <v>20769500</v>
+        <v>25159600</v>
       </c>
       <c r="J76" s="3">
+        <v>23113400</v>
+      </c>
+      <c r="K76" s="3">
         <v>21339900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22199700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21655800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21626500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22478300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22399400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21471800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21537500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>23211700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25037000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>26373700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>27406600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>27221500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>26445600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>27840900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>26597200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>26048900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24653900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>24249100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24117900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>23601100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>22829000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>22243300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>21616300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20977200</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6949,209 +7137,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>809800</v>
+        <v>615800</v>
       </c>
       <c r="E81" s="3">
-        <v>581200</v>
+        <v>901100</v>
       </c>
       <c r="F81" s="3">
-        <v>415600</v>
+        <v>646800</v>
       </c>
       <c r="G81" s="3">
-        <v>401700</v>
+        <v>462500</v>
       </c>
       <c r="H81" s="3">
-        <v>500300</v>
+        <v>447100</v>
       </c>
       <c r="I81" s="3">
-        <v>571700</v>
+        <v>556800</v>
       </c>
       <c r="J81" s="3">
+        <v>636200</v>
+      </c>
+      <c r="K81" s="3">
         <v>385300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>417400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>669300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>444200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>587400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>479300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>357100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>353100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>341200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>426900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>514300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>775900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>826500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>634000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>841200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>766100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>697700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>726700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>513000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>817400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>689400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>811000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>497800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>665000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7186,106 +7383,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>578700</v>
+      <c r="D83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E83" s="3">
-        <v>606300</v>
+        <v>644000</v>
       </c>
       <c r="F83" s="3">
-        <v>594000</v>
+        <v>674700</v>
       </c>
       <c r="G83" s="3">
-        <v>544800</v>
+        <v>1267400</v>
       </c>
       <c r="H83" s="3">
-        <v>593500</v>
+        <v>-1903100</v>
       </c>
       <c r="I83" s="3">
-        <v>594200</v>
+        <v>660500</v>
       </c>
       <c r="J83" s="3">
+        <v>661200</v>
+      </c>
+      <c r="K83" s="3">
         <v>543000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>553900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>554900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>567100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>595200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>600400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>568500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>592200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>607800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>656400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>708000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>673700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>696300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>678900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>745700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>706100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>672500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>643600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>698100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>625100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>610500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>596800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>583400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>562000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>551500</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7382,8 +7583,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7480,8 +7684,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7578,8 +7785,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7676,8 +7886,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7774,106 +7987,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>2021300</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E89" s="3">
-        <v>2140800</v>
+        <v>2249400</v>
       </c>
       <c r="F89" s="3">
-        <v>2514500</v>
+        <v>2382400</v>
       </c>
       <c r="G89" s="3">
-        <v>1256200</v>
+        <v>4196300</v>
       </c>
       <c r="H89" s="3">
-        <v>2127500</v>
+        <v>-5084900</v>
       </c>
       <c r="I89" s="3">
-        <v>2020700</v>
+        <v>2367600</v>
       </c>
       <c r="J89" s="3">
+        <v>2248700</v>
+      </c>
+      <c r="K89" s="3">
         <v>1879900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-214000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2243300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1184200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2698700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1608600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2407900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1732000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2631100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1552600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2834900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1711200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3255200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1636300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1980300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1020200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1637600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>884100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1772000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1193700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1172300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>803500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1250000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>994000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1888000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7908,8 +8127,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7935,79 +8155,82 @@
         <v>-254596000</v>
       </c>
       <c r="K91" s="3">
+        <v>-254596000</v>
+      </c>
+      <c r="L91" s="3">
         <v>-223427000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-248094000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-229768000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-256101000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-39500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-42700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-84600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-133300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-79200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-172200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-116600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-62600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-48600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-106500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-127700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-198600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-147500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-155900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-197500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-222200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2642900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2149200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2170900</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8104,8 +8327,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8202,106 +8428,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-1005100</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E94" s="3">
-        <v>-2267300</v>
+        <v>-1118600</v>
       </c>
       <c r="F94" s="3">
-        <v>-2872400</v>
+        <v>-2523200</v>
       </c>
       <c r="G94" s="3">
-        <v>-2613600</v>
+        <v>-6105100</v>
       </c>
       <c r="H94" s="3">
-        <v>-2595100</v>
+        <v>4890700</v>
       </c>
       <c r="I94" s="3">
-        <v>-1602400</v>
+        <v>-2888000</v>
       </c>
       <c r="J94" s="3">
+        <v>-1783200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1362800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1529700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-236300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2314500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2310200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-852200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2514400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3140600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1425100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2023400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3372700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3499800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3389900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3065100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1698000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3863100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2709000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>32500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-760600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1359900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>116900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1077700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1208800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-357200</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8336,8 +8568,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8345,97 +8578,100 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-317000</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-352800</v>
       </c>
       <c r="G96" s="3">
-        <v>-320300</v>
+        <v>-356500</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>398200</v>
       </c>
       <c r="I96" s="3">
-        <v>-322700</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-359200</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-375400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-322600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-385400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-320100</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-439200</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-408700</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-540100</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-363000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-454400</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-312700</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-345000</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-267500</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8532,8 +8768,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8630,8 +8869,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8728,298 +8970,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-209700</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E100" s="3">
-        <v>115200</v>
+        <v>-233400</v>
       </c>
       <c r="F100" s="3">
-        <v>273200</v>
+        <v>128200</v>
       </c>
       <c r="G100" s="3">
-        <v>-724100</v>
+        <v>-501700</v>
       </c>
       <c r="H100" s="3">
-        <v>2354500</v>
+        <v>-3917800</v>
       </c>
       <c r="I100" s="3">
-        <v>-170800</v>
+        <v>2620200</v>
       </c>
       <c r="J100" s="3">
+        <v>-190100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-271200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>933800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1715900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>192400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-205900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-350200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-356000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>131600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-216700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>852700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1587500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>927700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-136900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>197600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-769700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3671900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>352000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1637300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-330300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>571200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>434300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>622800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>713600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-108100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-426900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>88100</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E101" s="3">
-        <v>-47000</v>
+        <v>98100</v>
       </c>
       <c r="F101" s="3">
-        <v>44800</v>
+        <v>-52300</v>
       </c>
       <c r="G101" s="3">
-        <v>126300</v>
+        <v>190500</v>
       </c>
       <c r="H101" s="3">
-        <v>26400</v>
+        <v>-16900</v>
       </c>
       <c r="I101" s="3">
-        <v>-113500</v>
+        <v>29400</v>
       </c>
       <c r="J101" s="3">
+        <v>-126300</v>
+      </c>
+      <c r="K101" s="3">
         <v>79700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>157300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>111600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>39900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>8600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>83400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-39400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>51700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-35300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-58100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-69800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>49100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>10000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-82800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>24000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>42100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>41400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>141000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-42500</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>894600</v>
+      <c r="D102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E102" s="3">
-        <v>-58300</v>
+        <v>995500</v>
       </c>
       <c r="F102" s="3">
-        <v>-39800</v>
+        <v>-64900</v>
       </c>
       <c r="G102" s="3">
-        <v>-1955100</v>
+        <v>-2220000</v>
       </c>
       <c r="H102" s="3">
-        <v>1913300</v>
+        <v>-4128900</v>
       </c>
       <c r="I102" s="3">
-        <v>134000</v>
+        <v>2129200</v>
       </c>
       <c r="J102" s="3">
+        <v>149100</v>
+      </c>
+      <c r="K102" s="3">
         <v>325600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-652600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>402700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-898100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>186600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>414800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-379100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1277400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>989800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>383500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1010300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-809300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-306900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1289300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-496100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>759200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-670400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-710700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>798800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>424100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-166800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1487500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>874100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-181900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1061400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>IX</t>
   </si>
@@ -656,437 +656,450 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5027800</v>
+        <v>4854600</v>
       </c>
       <c r="E8" s="3">
-        <v>5513200</v>
+        <v>4402000</v>
       </c>
       <c r="F8" s="3">
-        <v>4814700</v>
+        <v>5133700</v>
       </c>
       <c r="G8" s="3">
-        <v>4847600</v>
+        <v>4810700</v>
       </c>
       <c r="H8" s="3">
-        <v>4805300</v>
+        <v>4572700</v>
       </c>
       <c r="I8" s="3">
-        <v>4748600</v>
+        <v>4682200</v>
       </c>
       <c r="J8" s="3">
+        <v>5031200</v>
+      </c>
+      <c r="K8" s="3">
         <v>4473200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4510700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4433700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4331000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4304600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4561900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4474800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4445500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4258400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4261900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4586100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5250300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5208200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5394500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5023800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6138000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5042300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6113700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5489600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6037700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6120900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6558500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7162400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6678100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6250200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5616300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2933200</v>
+        <v>2662700</v>
       </c>
       <c r="E9" s="3">
-        <v>3227100</v>
+        <v>2583600</v>
       </c>
       <c r="F9" s="3">
-        <v>2654400</v>
+        <v>3049700</v>
       </c>
       <c r="G9" s="3">
-        <v>2795000</v>
+        <v>2692600</v>
       </c>
       <c r="H9" s="3">
-        <v>2820800</v>
+        <v>2673800</v>
       </c>
       <c r="I9" s="3">
-        <v>2722600</v>
+        <v>2768100</v>
       </c>
       <c r="J9" s="3">
+        <v>2887700</v>
+      </c>
+      <c r="K9" s="3">
         <v>2456800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2983700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2816500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2792900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2639600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2863300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2678900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2911600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2651900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2623600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2965900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3323400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3188900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3275300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2984300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3960200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3109200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3952000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3459500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4148400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4173600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4727200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5316600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4878500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4517300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3914700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2094600</v>
+        <v>2191900</v>
       </c>
       <c r="E10" s="3">
-        <v>2286000</v>
+        <v>1818400</v>
       </c>
       <c r="F10" s="3">
-        <v>2160200</v>
+        <v>2084000</v>
       </c>
       <c r="G10" s="3">
-        <v>2052600</v>
+        <v>2118100</v>
       </c>
       <c r="H10" s="3">
-        <v>1984400</v>
+        <v>1898900</v>
       </c>
       <c r="I10" s="3">
-        <v>2026000</v>
+        <v>1914100</v>
       </c>
       <c r="J10" s="3">
+        <v>2143500</v>
+      </c>
+      <c r="K10" s="3">
         <v>2016400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1527000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1617200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1538100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1665000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1698700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1795800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1534000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1606500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1638300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1620200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1926900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2019300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2119200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2039500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2177800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1933100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2161700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2030100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1889300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1947200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1831300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1845700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1799600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1732900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1701600</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1122,8 +1135,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1324,210 +1341,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-395200</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-38100</v>
+      </c>
+      <c r="K14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L14" s="3">
+        <v>900</v>
+      </c>
+      <c r="M14" s="3">
+        <v>700</v>
+      </c>
+      <c r="N14" s="3">
+        <v>136800</v>
+      </c>
+      <c r="O14" s="3">
+        <v>102900</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3">
-        <v>7700</v>
-      </c>
-      <c r="F14" s="3">
-        <v>700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H14" s="3">
-        <v>600</v>
-      </c>
-      <c r="I14" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J14" s="3">
-        <v>3800</v>
-      </c>
-      <c r="K14" s="3">
-        <v>900</v>
-      </c>
-      <c r="L14" s="3">
-        <v>700</v>
-      </c>
-      <c r="M14" s="3">
-        <v>136800</v>
-      </c>
-      <c r="N14" s="3">
-        <v>102900</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>13000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-35000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>22500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>23000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>22600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>14100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>3500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>9800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>38400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>30100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="3">
+        <v>700800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>566100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>599700</v>
+      </c>
+      <c r="G15" s="3">
+        <v>674200</v>
+      </c>
+      <c r="H15" s="3">
+        <v>623400</v>
+      </c>
+      <c r="I15" s="3">
+        <v>590600</v>
+      </c>
+      <c r="J15" s="3">
+        <v>669700</v>
+      </c>
+      <c r="K15" s="3">
+        <v>15700</v>
+      </c>
+      <c r="L15" s="3">
+        <v>13900</v>
+      </c>
+      <c r="M15" s="3">
+        <v>14600</v>
+      </c>
+      <c r="N15" s="3">
+        <v>15400</v>
+      </c>
+      <c r="O15" s="3">
+        <v>16000</v>
+      </c>
+      <c r="P15" s="3">
+        <v>14800</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>17500</v>
+      </c>
+      <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="3">
-        <v>17900</v>
-      </c>
-      <c r="F15" s="3">
-        <v>16600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>16100</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="S15" s="3">
         <v>15100</v>
       </c>
-      <c r="I15" s="3">
-        <v>12900</v>
-      </c>
-      <c r="J15" s="3">
-        <v>15700</v>
-      </c>
-      <c r="K15" s="3">
-        <v>13900</v>
-      </c>
-      <c r="L15" s="3">
-        <v>14600</v>
-      </c>
-      <c r="M15" s="3">
-        <v>15400</v>
-      </c>
-      <c r="N15" s="3">
-        <v>16000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>14800</v>
-      </c>
-      <c r="P15" s="3">
-        <v>17500</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="3">
-        <v>15100</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>16500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>16700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>20100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>17200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>16400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>16200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>13200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>12500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>10500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>9900</v>
-      </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF15" s="3">
         <v>11400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>11000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>13300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>11900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1560,210 +1586,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4415300</v>
+        <v>4204000</v>
       </c>
       <c r="E17" s="3">
-        <v>4799500</v>
+        <v>3585500</v>
       </c>
       <c r="F17" s="3">
-        <v>4131900</v>
+        <v>4070400</v>
       </c>
       <c r="G17" s="3">
-        <v>4274000</v>
+        <v>3858000</v>
       </c>
       <c r="H17" s="3">
-        <v>4215900</v>
+        <v>3697900</v>
       </c>
       <c r="I17" s="3">
-        <v>4065400</v>
+        <v>3860600</v>
       </c>
       <c r="J17" s="3">
+        <v>3656800</v>
+      </c>
+      <c r="K17" s="3">
         <v>3834400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4082800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3868600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4198400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3801700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3790900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3725200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3979600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3717000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3682900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4160600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4960500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4524800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4603700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4330800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5453200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4446700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5155900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4653400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5469000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5359200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5681200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6330900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5953800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5529800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4916200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>612500</v>
+        <v>650600</v>
       </c>
       <c r="E18" s="3">
-        <v>713700</v>
+        <v>816600</v>
       </c>
       <c r="F18" s="3">
-        <v>682800</v>
+        <v>1063400</v>
       </c>
       <c r="G18" s="3">
-        <v>573600</v>
+        <v>952700</v>
       </c>
       <c r="H18" s="3">
-        <v>589300</v>
+        <v>874700</v>
       </c>
       <c r="I18" s="3">
-        <v>683100</v>
+        <v>821600</v>
       </c>
       <c r="J18" s="3">
+        <v>1374400</v>
+      </c>
+      <c r="K18" s="3">
         <v>638800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>427900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>565100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>132600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>502900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>771000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>749500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>465900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>541400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>579000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>425500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>289800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>683400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>790800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>693000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>684800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>595600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>957800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>836200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>568700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>761700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>877300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>831500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>724300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>720400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>700100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1799,233 +1832,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>240700</v>
+        <v>-541700</v>
       </c>
       <c r="E20" s="3">
-        <v>422100</v>
+        <v>-48200</v>
       </c>
       <c r="F20" s="3">
-        <v>208600</v>
+        <v>73000</v>
       </c>
       <c r="G20" s="3">
-        <v>101500</v>
+        <v>-222800</v>
       </c>
       <c r="H20" s="3">
-        <v>45400</v>
+        <v>-67000</v>
       </c>
       <c r="I20" s="3">
-        <v>70500</v>
+        <v>-88700</v>
       </c>
       <c r="J20" s="3">
+        <v>320600</v>
+      </c>
+      <c r="K20" s="3">
         <v>212500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>86100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1117000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>155900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>99500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>87000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>11300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-60600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>151400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>257300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>426400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>401800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>212600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>281600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>105100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>64000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>172300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>109400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>213500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>180400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>394400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>81700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>298400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>1893100</v>
       </c>
       <c r="E21" s="3">
-        <v>1779800</v>
+        <v>1430900</v>
       </c>
       <c r="F21" s="3">
-        <v>1566100</v>
+        <v>1590000</v>
       </c>
       <c r="G21" s="3">
-        <v>1942400</v>
+        <v>1849600</v>
       </c>
       <c r="H21" s="3">
-        <v>-1268400</v>
+        <v>1565100</v>
       </c>
       <c r="I21" s="3">
-        <v>1414100</v>
+        <v>1501000</v>
       </c>
       <c r="J21" s="3">
+        <v>1723600</v>
+      </c>
+      <c r="K21" s="3">
         <v>1512500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1056900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1130600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1804400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1225900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1465700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1335800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1121400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1144900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1126200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1233300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1255100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1783600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1888900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1584500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1712100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1406800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1694300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1652200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1376200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1600300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1668200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1822700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1389400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1580800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1445600</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>270200</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>279800</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>327900</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>338700</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>320100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>298000</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>293400</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2102,210 +2142,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>853200</v>
+        <v>955000</v>
       </c>
       <c r="E23" s="3">
-        <v>1135800</v>
+        <v>747000</v>
       </c>
       <c r="F23" s="3">
-        <v>891300</v>
+        <v>1057600</v>
       </c>
       <c r="G23" s="3">
-        <v>675000</v>
+        <v>890600</v>
       </c>
       <c r="H23" s="3">
-        <v>634700</v>
+        <v>636500</v>
       </c>
       <c r="I23" s="3">
-        <v>753700</v>
+        <v>618300</v>
       </c>
       <c r="J23" s="3">
+        <v>798500</v>
+      </c>
+      <c r="K23" s="3">
         <v>851300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>514000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>576700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1249600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>658800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>870500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>735400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>552900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>552700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>518400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>576900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>547100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1109900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1192600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>905600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>966400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>700700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1021800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1008600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>678100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>975200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1057700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1225900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>806000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>894100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>248500</v>
+        <v>278200</v>
       </c>
       <c r="E24" s="3">
-        <v>276900</v>
+        <v>217600</v>
       </c>
       <c r="F24" s="3">
-        <v>273700</v>
+        <v>257900</v>
       </c>
       <c r="G24" s="3">
-        <v>203000</v>
+        <v>273500</v>
       </c>
       <c r="H24" s="3">
-        <v>179200</v>
+        <v>191400</v>
       </c>
       <c r="I24" s="3">
+        <v>174500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>198700</v>
+      </c>
+      <c r="K24" s="3">
+        <v>204900</v>
+      </c>
+      <c r="L24" s="3">
+        <v>119700</v>
+      </c>
+      <c r="M24" s="3">
+        <v>143000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>574000</v>
+      </c>
+      <c r="O24" s="3">
+        <v>226000</v>
+      </c>
+      <c r="P24" s="3">
+        <v>278400</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>216500</v>
+      </c>
+      <c r="R24" s="3">
+        <v>179500</v>
+      </c>
+      <c r="S24" s="3">
         <v>187500</v>
       </c>
-      <c r="J24" s="3">
-        <v>204900</v>
-      </c>
-      <c r="K24" s="3">
-        <v>119700</v>
-      </c>
-      <c r="L24" s="3">
-        <v>143000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>574000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>226000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>278400</v>
-      </c>
-      <c r="P24" s="3">
-        <v>216500</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>179500</v>
-      </c>
-      <c r="R24" s="3">
-        <v>187500</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>167500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>146500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>86600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>325100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>349300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>265200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>120600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-77300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>310300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>281100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>135400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>142100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>348400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>403800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>300000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>336300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>295100</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2405,210 +2454,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>604700</v>
+        <v>676800</v>
       </c>
       <c r="E26" s="3">
-        <v>858800</v>
+        <v>529400</v>
       </c>
       <c r="F26" s="3">
-        <v>617600</v>
+        <v>799700</v>
       </c>
       <c r="G26" s="3">
-        <v>472000</v>
+        <v>617100</v>
       </c>
       <c r="H26" s="3">
-        <v>455500</v>
+        <v>445100</v>
       </c>
       <c r="I26" s="3">
-        <v>566200</v>
+        <v>443700</v>
       </c>
       <c r="J26" s="3">
+        <v>599900</v>
+      </c>
+      <c r="K26" s="3">
         <v>646400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>394200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>433700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>675600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>432900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>592100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>518900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>373300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>365200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>350800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>430400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>460500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>784800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>843300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>640300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>845800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>777900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>711500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>727500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>542700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>833100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>709300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>822100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>506000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>682500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>599000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>615800</v>
+        <v>671500</v>
       </c>
       <c r="E27" s="3">
-        <v>901100</v>
+        <v>539200</v>
       </c>
       <c r="F27" s="3">
-        <v>646800</v>
+        <v>839200</v>
       </c>
       <c r="G27" s="3">
-        <v>462500</v>
+        <v>646300</v>
       </c>
       <c r="H27" s="3">
-        <v>447100</v>
+        <v>436100</v>
       </c>
       <c r="I27" s="3">
-        <v>556800</v>
+        <v>435500</v>
       </c>
       <c r="J27" s="3">
+        <v>589900</v>
+      </c>
+      <c r="K27" s="3">
         <v>636200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>385300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>417400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>668300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>444200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>587400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>479300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>365300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>353100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>341200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>426900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>455800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>775900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>826500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>634000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>841200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>766100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>697700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>726700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>513000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>817400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>689400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>811000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>497800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>665000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2708,31 +2766,34 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -2740,11 +2801,11 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="3">
         <v>900</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
@@ -2752,11 +2813,11 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3">
         <v>-8200</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2764,11 +2825,11 @@
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3">
         <v>58500</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2782,14 +2843,14 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2800,8 +2861,8 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
@@ -2809,8 +2870,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2910,8 +2974,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3011,210 +3078,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-240700</v>
+        <v>541700</v>
       </c>
       <c r="E32" s="3">
-        <v>-422100</v>
+        <v>48200</v>
       </c>
       <c r="F32" s="3">
-        <v>-208600</v>
+        <v>-73000</v>
       </c>
       <c r="G32" s="3">
-        <v>-101500</v>
+        <v>222800</v>
       </c>
       <c r="H32" s="3">
-        <v>-45400</v>
+        <v>67000</v>
       </c>
       <c r="I32" s="3">
-        <v>-70500</v>
+        <v>88700</v>
       </c>
       <c r="J32" s="3">
+        <v>-320600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-212500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-86100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1117000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-155900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-99500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>14100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-87000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-11300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>60600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-151400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-257300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-426400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-401800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-212600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-281600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-105100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-64000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-172300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-109400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-213500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-180400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-394400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-81700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-298400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-194000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>615800</v>
+        <v>671600</v>
       </c>
       <c r="E33" s="3">
-        <v>901100</v>
+        <v>539200</v>
       </c>
       <c r="F33" s="3">
-        <v>646800</v>
+        <v>839200</v>
       </c>
       <c r="G33" s="3">
-        <v>462500</v>
+        <v>646300</v>
       </c>
       <c r="H33" s="3">
-        <v>447100</v>
+        <v>436100</v>
       </c>
       <c r="I33" s="3">
-        <v>556800</v>
+        <v>435500</v>
       </c>
       <c r="J33" s="3">
+        <v>589900</v>
+      </c>
+      <c r="K33" s="3">
         <v>636200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>385300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>417400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>669300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>444200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>587400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>479300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>357100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>353100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>341200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>426900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>514300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>775900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>826500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>634000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>841200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>766100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>697700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>726700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>513000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>817400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>689400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>811000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>497800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>665000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3314,215 +3390,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>615800</v>
+        <v>671600</v>
       </c>
       <c r="E35" s="3">
-        <v>901100</v>
+        <v>539200</v>
       </c>
       <c r="F35" s="3">
-        <v>646800</v>
+        <v>839200</v>
       </c>
       <c r="G35" s="3">
-        <v>462500</v>
+        <v>646300</v>
       </c>
       <c r="H35" s="3">
-        <v>447100</v>
+        <v>436100</v>
       </c>
       <c r="I35" s="3">
-        <v>556800</v>
+        <v>435500</v>
       </c>
       <c r="J35" s="3">
+        <v>589900</v>
+      </c>
+      <c r="K35" s="3">
         <v>636200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>385300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>417400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>669300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>444200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>587400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>479300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>357100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>353100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>341200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>426900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>514300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>775900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>826500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>634000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>841200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>766100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>697700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>726700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>513000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>817400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>689400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>811000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>497800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>665000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3558,8 +3643,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3595,132 +3681,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8212500</v>
+        <v>8159400</v>
       </c>
       <c r="E41" s="3">
-        <v>8415700</v>
+        <v>6171300</v>
       </c>
       <c r="F41" s="3">
-        <v>7420200</v>
+        <v>6828300</v>
       </c>
       <c r="G41" s="3">
-        <v>7485000</v>
+        <v>6415100</v>
       </c>
       <c r="H41" s="3">
-        <v>7529300</v>
+        <v>6126800</v>
       </c>
       <c r="I41" s="3">
-        <v>9705000</v>
+        <v>6378400</v>
       </c>
       <c r="J41" s="3">
+        <v>9266700</v>
+      </c>
+      <c r="K41" s="3">
         <v>7575800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6673600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6706200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7249600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7084100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8377200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8349700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7654200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8305200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10183900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10067500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10001900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9297700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10195800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10468300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12335200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12604300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11656800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12061800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12702300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11964900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11518800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>11731700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>10051600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>9284500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>9275800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>126600</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>139000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>198100</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>226300</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>213000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>220800</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3797,233 +3887,242 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2301500</v>
+        <v>37039000</v>
       </c>
       <c r="E43" s="3">
-        <v>2437100</v>
+        <v>33602900</v>
       </c>
       <c r="F43" s="3">
-        <v>2225800</v>
+        <v>36547700</v>
       </c>
       <c r="G43" s="3">
-        <v>2163600</v>
+        <v>38203900</v>
       </c>
       <c r="H43" s="3">
-        <v>2566100</v>
+        <v>36401600</v>
       </c>
       <c r="I43" s="3">
-        <v>2672700</v>
+        <v>37888900</v>
       </c>
       <c r="J43" s="3">
+        <v>40837100</v>
+      </c>
+      <c r="K43" s="3">
         <v>2136000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1849700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2251200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1928900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1578100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1519400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1779900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1952500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1566800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1312300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1704500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2254500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1999500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1879200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2136800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2139000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1930100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2040800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2255700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2170500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2281800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1973500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1850500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1988700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1868400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1833400</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1543600</v>
+        <v>1514100</v>
       </c>
       <c r="E44" s="3">
-        <v>1614200</v>
+        <v>1351500</v>
       </c>
       <c r="F44" s="3">
-        <v>1641400</v>
+        <v>1503200</v>
       </c>
       <c r="G44" s="3">
-        <v>1582600</v>
+        <v>1640100</v>
       </c>
       <c r="H44" s="3">
-        <v>1207100</v>
+        <v>1492400</v>
       </c>
       <c r="I44" s="3">
-        <v>1200000</v>
+        <v>1175900</v>
       </c>
       <c r="J44" s="3">
+        <v>1271500</v>
+      </c>
+      <c r="K44" s="3">
         <v>1036000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>986100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>987100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>926700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>948200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>958100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1006200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1007900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1080000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1053500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1105000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1110200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1202100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1161000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1146700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1111800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1369000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1220500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1117200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1003400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1246700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1174100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1116500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1045400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1265400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1328700</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
+        <v>341300</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>384100</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>495400</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>708000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>373100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4100,31 +4199,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>48120300</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>42144800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>46383400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>47840200</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>45673900</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>47320300</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>52985100</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4201,242 +4303,251 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>60544200</v>
+        <v>30723000</v>
       </c>
       <c r="E47" s="3">
-        <v>60604000</v>
+        <v>28805900</v>
       </c>
       <c r="F47" s="3">
-        <v>58693400</v>
+        <v>29193900</v>
       </c>
       <c r="G47" s="3">
-        <v>58531800</v>
+        <v>30071400</v>
       </c>
       <c r="H47" s="3">
-        <v>58016400</v>
+        <v>27829000</v>
       </c>
       <c r="I47" s="3">
-        <v>55710800</v>
+        <v>28075100</v>
       </c>
       <c r="J47" s="3">
+        <v>28293500</v>
+      </c>
+      <c r="K47" s="3">
         <v>55010700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>51027800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>53430500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>51081400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>52315800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>52503500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>52973200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>51182600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>51463300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>53541500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>58386100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>59973800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>74441200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>71989200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>69844300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>82078400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>78817700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>75266400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>69855700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>69467000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>71014900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>70684000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>70420000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>69927900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>70281800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>67221000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>21182600</v>
+        <v>6569600</v>
       </c>
       <c r="E48" s="3">
-        <v>19926900</v>
+        <v>5910300</v>
       </c>
       <c r="F48" s="3">
-        <v>18701000</v>
+        <v>6779200</v>
       </c>
       <c r="G48" s="3">
-        <v>18538600</v>
+        <v>6461400</v>
       </c>
       <c r="H48" s="3">
-        <v>18031300</v>
+        <v>5943500</v>
       </c>
       <c r="I48" s="3">
-        <v>23333900</v>
+        <v>6094500</v>
       </c>
       <c r="J48" s="3">
+        <v>7319900</v>
+      </c>
+      <c r="K48" s="3">
         <v>16212000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14530600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15370200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15042700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15489200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16390700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15748800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15218300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>16071400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16625000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>18395500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19086100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6587600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6033700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6371700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5285700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5647800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5234600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5009900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4951600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4682600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4655100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4632500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4521200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4311900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4267300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>8</v>
+      <c r="D49" s="3">
+        <v>8517000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>8397800</v>
+        <v>8227500</v>
       </c>
       <c r="G49" s="3">
-        <v>8557000</v>
+        <v>8927300</v>
       </c>
       <c r="H49" s="3">
-        <v>8135400</v>
+        <v>8608000</v>
       </c>
       <c r="I49" s="3">
-        <v>8483800</v>
+        <v>8806500</v>
       </c>
       <c r="J49" s="3">
+        <v>9163100</v>
+      </c>
+      <c r="K49" s="3">
         <v>6633600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6103600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6015300</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>8</v>
@@ -4450,8 +4561,8 @@
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -4504,8 +4615,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4605,8 +4719,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4706,31 +4823,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>20125100</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>25723600</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>16887500</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>16449000</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>15698900</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>15455000</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>16890000</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4807,8 +4927,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4908,109 +5031,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>117166800</v>
+        <v>114055000</v>
       </c>
       <c r="E54" s="3">
-        <v>115886900</v>
+        <v>102584500</v>
       </c>
       <c r="F54" s="3">
-        <v>111961200</v>
+        <v>107911100</v>
       </c>
       <c r="G54" s="3">
-        <v>112146100</v>
+        <v>111868400</v>
       </c>
       <c r="H54" s="3">
-        <v>110647400</v>
+        <v>105751300</v>
       </c>
       <c r="I54" s="3">
-        <v>108554600</v>
+        <v>107785400</v>
       </c>
       <c r="J54" s="3">
+        <v>115014900</v>
+      </c>
+      <c r="K54" s="3">
         <v>103332600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>94334700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>98555600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>94757300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>96806300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>99748000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>99827500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>96162300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>97668500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>102579300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>111679100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>115124900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>116999300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>114976800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>113629300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>117001000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>114429700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>109422700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>103370600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>103290900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>104429300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>103291400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>102314200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>99626900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>98834300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>95642500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5046,8 +5175,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5083,334 +5213,344 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2294100</v>
+        <v>2075400</v>
       </c>
       <c r="E57" s="3">
-        <v>2573800</v>
+        <v>2008500</v>
       </c>
       <c r="F57" s="3">
-        <v>2346900</v>
+        <v>2396600</v>
       </c>
       <c r="G57" s="3">
-        <v>2341900</v>
+        <v>2345000</v>
       </c>
       <c r="H57" s="3">
-        <v>2236400</v>
+        <v>2208300</v>
       </c>
       <c r="I57" s="3">
-        <v>2604600</v>
+        <v>2178600</v>
       </c>
       <c r="J57" s="3">
+        <v>2759600</v>
+      </c>
+      <c r="K57" s="3">
         <v>1794600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1585600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1774500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1935000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1556000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1660300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1546400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1848400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1558500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1535100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1627400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2490800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2067100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2140100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2032100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2820300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2206000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2131700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2416200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2371200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1898700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1915700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1891500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2233500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1846800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1846700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4558700</v>
+        <v>5220900</v>
       </c>
       <c r="E58" s="3">
-        <v>4076100</v>
+        <v>3991300</v>
       </c>
       <c r="F58" s="3">
-        <v>4593000</v>
+        <v>9984300</v>
       </c>
       <c r="G58" s="3">
-        <v>4163300</v>
+        <v>4615500</v>
       </c>
       <c r="H58" s="3">
-        <v>4085000</v>
+        <v>3947200</v>
       </c>
       <c r="I58" s="3">
-        <v>3612500</v>
+        <v>4005700</v>
       </c>
       <c r="J58" s="3">
+        <v>3852400</v>
+      </c>
+      <c r="K58" s="3">
         <v>3163300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2945500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3984500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2919200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4574600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3561600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3355000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2178500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2722800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2816300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3217100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2967500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3499400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2525500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3084300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2974800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6124400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3014300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2165000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2773100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3241500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3034400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3398100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2514400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2628100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1852200</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>19427400</v>
+        <v>4414400</v>
       </c>
       <c r="E59" s="3">
-        <v>21771800</v>
+        <v>3381700</v>
       </c>
       <c r="F59" s="3">
-        <v>19436000</v>
+        <v>7861700</v>
       </c>
       <c r="G59" s="3">
-        <v>19251900</v>
+        <v>4082900</v>
       </c>
       <c r="H59" s="3">
-        <v>19338700</v>
+        <v>3918700</v>
       </c>
       <c r="I59" s="3">
-        <v>23711200</v>
+        <v>4363600</v>
       </c>
       <c r="J59" s="3">
+        <v>701400</v>
+      </c>
+      <c r="K59" s="3">
         <v>18750000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16383500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17574500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20002500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18559000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19455100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19718700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21080400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19858200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>20846200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>22491300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>22800700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>23138900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>22619100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21575000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21945200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>21264700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>21021000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>19682100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>19204700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>19329900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>19044800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>18495000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>18275000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>17244500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>16647500</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>11710800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>9381600</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>20242600</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>11043400</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>10074300</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>10547800</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>7313500</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5487,132 +5627,138 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>40779000</v>
+        <v>38353200</v>
       </c>
       <c r="E61" s="3">
-        <v>40003200</v>
+        <v>35703700</v>
       </c>
       <c r="F61" s="3">
-        <v>37869400</v>
+        <v>32754200</v>
       </c>
       <c r="G61" s="3">
-        <v>38682500</v>
+        <v>37838000</v>
       </c>
       <c r="H61" s="3">
-        <v>37458600</v>
+        <v>36476800</v>
       </c>
       <c r="I61" s="3">
-        <v>37039600</v>
+        <v>36489700</v>
       </c>
       <c r="J61" s="3">
+        <v>41356500</v>
+      </c>
+      <c r="K61" s="3">
         <v>33794000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31572800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31785500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>29446700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>29889600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>31374300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>31744800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>31339600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31786500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>33212400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>37004500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>37701100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>37525700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>37410700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>37668500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>40229600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>37481900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>35869000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>34202200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>34591600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>35174700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>34962700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>35088200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>34193700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>34384900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>33751200</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>35953600</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>31643700</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>24633400</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>35752500</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>33269900</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>34787700</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>35535300</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5689,8 +5835,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5790,8 +5939,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5891,8 +6043,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5992,109 +6147,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>88243900</v>
+        <v>86264300</v>
       </c>
       <c r="E66" s="3">
-        <v>87902500</v>
+        <v>76729000</v>
       </c>
       <c r="F66" s="3">
-        <v>85496700</v>
+        <v>81303000</v>
       </c>
       <c r="G66" s="3">
-        <v>85442300</v>
+        <v>84862100</v>
       </c>
       <c r="H66" s="3">
-        <v>84780000</v>
+        <v>80016200</v>
       </c>
       <c r="I66" s="3">
-        <v>83395000</v>
+        <v>82031300</v>
       </c>
       <c r="J66" s="3">
+        <v>87818900</v>
+      </c>
+      <c r="K66" s="3">
         <v>80219200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>72994800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>76355800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>73101400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>75179800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>77269700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>77428100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>74690500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>76131100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>79367500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>86642100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>88751200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>89592700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>87755300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>87183700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>89160100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>87832500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>83373800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>78716600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>79041800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>80311500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>79690300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>79485200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>77383600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>77218100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>74665300</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6130,8 +6291,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6231,8 +6393,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6332,8 +6497,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6433,8 +6601,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6534,109 +6705,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>23301500</v>
+        <v>23579600</v>
       </c>
       <c r="E72" s="3">
-        <v>23144100</v>
+        <v>20401500</v>
       </c>
       <c r="F72" s="3">
-        <v>22533700</v>
+        <v>21551200</v>
       </c>
       <c r="G72" s="3">
-        <v>22239600</v>
+        <v>22515000</v>
       </c>
       <c r="H72" s="3">
-        <v>21777200</v>
+        <v>20971500</v>
       </c>
       <c r="I72" s="3">
-        <v>21686600</v>
+        <v>21213900</v>
       </c>
       <c r="J72" s="3">
+        <v>22977200</v>
+      </c>
+      <c r="K72" s="3">
         <v>21402300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18983000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19650300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19317900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19625900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20469500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20268200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>19459100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>20219500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>21453300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>23117700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>24266800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>24561300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>24406600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>23503000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>24559200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>23318000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>22550800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>21382600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>20930200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>20440400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19935700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19246400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18427200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>17917900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>17520500</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6736,8 +6913,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6837,8 +7017,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6938,109 +7121,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>28922900</v>
+        <v>27237800</v>
       </c>
       <c r="E76" s="3">
-        <v>27984400</v>
+        <v>25323200</v>
       </c>
       <c r="F76" s="3">
-        <v>26464600</v>
+        <v>26058400</v>
       </c>
       <c r="G76" s="3">
-        <v>26703800</v>
+        <v>26442600</v>
       </c>
       <c r="H76" s="3">
-        <v>25867500</v>
+        <v>25181100</v>
       </c>
       <c r="I76" s="3">
-        <v>25159600</v>
+        <v>25198400</v>
       </c>
       <c r="J76" s="3">
+        <v>26656900</v>
+      </c>
+      <c r="K76" s="3">
         <v>23113400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21339900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22199700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21655800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21626500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22478300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22399400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21471800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21537500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23211700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25037000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>26373700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>27406600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>27221500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>26445600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>27840900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>26597200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>26048900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>24653900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24249100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>24117900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>23601100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>22829000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>22243300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>21616300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20977200</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7140,215 +7329,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>615800</v>
+        <v>671600</v>
       </c>
       <c r="E81" s="3">
-        <v>901100</v>
+        <v>539200</v>
       </c>
       <c r="F81" s="3">
-        <v>646800</v>
+        <v>839200</v>
       </c>
       <c r="G81" s="3">
-        <v>462500</v>
+        <v>646300</v>
       </c>
       <c r="H81" s="3">
-        <v>447100</v>
+        <v>436100</v>
       </c>
       <c r="I81" s="3">
-        <v>556800</v>
+        <v>435500</v>
       </c>
       <c r="J81" s="3">
+        <v>589900</v>
+      </c>
+      <c r="K81" s="3">
         <v>636200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>385300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>417400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>669300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>444200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>587400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>479300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>357100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>353100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>341200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>426900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>514300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>775900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>826500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>634000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>841200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>766100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>697700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>726700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>513000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>817400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>689400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>811000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>497800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>665000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7384,109 +7582,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>623400</v>
       </c>
       <c r="E83" s="3">
-        <v>644000</v>
+        <v>590600</v>
       </c>
       <c r="F83" s="3">
-        <v>674700</v>
+        <v>412400</v>
       </c>
       <c r="G83" s="3">
-        <v>1267400</v>
+        <v>687800</v>
       </c>
       <c r="H83" s="3">
-        <v>-1903100</v>
+        <v>561400</v>
       </c>
       <c r="I83" s="3">
-        <v>660500</v>
+        <v>583400</v>
       </c>
       <c r="J83" s="3">
+        <v>688200</v>
+      </c>
+      <c r="K83" s="3">
         <v>661200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>543000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>553900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>554900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>567100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>595200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>600400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>568500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>592200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>607800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>656400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>708000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>673700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>696300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>678900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>745700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>706100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>672500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>643600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>698100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>625100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>610500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>596800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>583400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>562000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>551500</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7586,8 +7788,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7687,8 +7892,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7788,8 +7996,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7889,8 +8100,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7990,109 +8204,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E89" s="3">
-        <v>2249400</v>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F89" s="3">
-        <v>2382400</v>
+        <v>2094600</v>
       </c>
       <c r="G89" s="3">
-        <v>4196300</v>
+        <v>2380500</v>
       </c>
       <c r="H89" s="3">
-        <v>-5084900</v>
+        <v>2638800</v>
       </c>
       <c r="I89" s="3">
-        <v>2367600</v>
+        <v>1361800</v>
       </c>
       <c r="J89" s="3">
+        <v>2508500</v>
+      </c>
+      <c r="K89" s="3">
         <v>2248700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1879900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-214000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2243300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1184200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2698700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1608600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2407900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1732000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2631100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1552600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2834900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1711200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3255200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1636300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1980300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1020200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1637600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>884100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1772000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1193700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1172300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>803500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1250000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>994000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1888000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8128,109 +8348,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-250633000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-292529000</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F91" s="3">
-        <v>-336475000</v>
+        <v>-1657000</v>
       </c>
       <c r="G91" s="3">
-        <v>-321237000</v>
+        <v>-2075200</v>
       </c>
       <c r="H91" s="3">
-        <v>-303186000</v>
+        <v>-2252700</v>
       </c>
       <c r="I91" s="3">
-        <v>-298865000</v>
+        <v>-2221800</v>
       </c>
       <c r="J91" s="3">
-        <v>-254596000</v>
+        <v>-2280700</v>
       </c>
       <c r="K91" s="3">
         <v>-254596000</v>
       </c>
       <c r="L91" s="3">
+        <v>-254596000</v>
+      </c>
+      <c r="M91" s="3">
         <v>-223427000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-248094000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-229768000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-256101000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-39500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-42700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-84600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-133300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-79200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-172200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-116600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-62600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-48600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-106500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-127700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-198600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-147500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-155900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-197500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-222200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2642900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2149200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2170900</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8330,8 +8554,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8431,109 +8658,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="3">
-        <v>-1118600</v>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F94" s="3">
-        <v>-2523200</v>
+        <v>-1041600</v>
       </c>
       <c r="G94" s="3">
-        <v>-6105100</v>
+        <v>-2521100</v>
       </c>
       <c r="H94" s="3">
-        <v>4890700</v>
+        <v>-3014300</v>
       </c>
       <c r="I94" s="3">
-        <v>-2888000</v>
+        <v>-2833300</v>
       </c>
       <c r="J94" s="3">
+        <v>-3059900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1783200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1362800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1529700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-236300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2314500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2310200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-852200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2514400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3140600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1425100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2023400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3372700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3499800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3389900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3065100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1698000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3863100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2709000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>32500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-760600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1359900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>116900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1077700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1208800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-357200</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8569,109 +8802,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F96" s="3">
-        <v>-352800</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-356500</v>
+        <v>352500</v>
       </c>
       <c r="H96" s="3">
-        <v>398200</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>347300</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-359200</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-375400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-322600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-385400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-320100</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-439200</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-408700</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-540100</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-363000</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-454400</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-312700</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-345000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-267500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8771,8 +9008,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8872,8 +9112,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8973,307 +9216,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E100" s="3">
-        <v>-233400</v>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F100" s="3">
-        <v>128200</v>
+        <v>-217400</v>
       </c>
       <c r="G100" s="3">
-        <v>-501700</v>
+        <v>128100</v>
       </c>
       <c r="H100" s="3">
-        <v>-3917800</v>
+        <v>286700</v>
       </c>
       <c r="I100" s="3">
-        <v>2620200</v>
+        <v>-784900</v>
       </c>
       <c r="J100" s="3">
+        <v>2776100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-190100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-271200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>933800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1715900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>192400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-205900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-350200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-356000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>131600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-216700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>852700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1587500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>927700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-136900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>197600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-769700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3671900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>352000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1637300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-330300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>571200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>434300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>622800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>713600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-108100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-426900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>47100</v>
       </c>
       <c r="E101" s="3">
-        <v>98100</v>
+        <v>136900</v>
       </c>
       <c r="F101" s="3">
-        <v>-52300</v>
+        <v>31200</v>
       </c>
       <c r="G101" s="3">
-        <v>190500</v>
+        <v>-134900</v>
       </c>
       <c r="H101" s="3">
-        <v>-16900</v>
+        <v>86300</v>
       </c>
       <c r="I101" s="3">
-        <v>29400</v>
+        <v>171700</v>
       </c>
       <c r="J101" s="3">
+        <v>138400</v>
+      </c>
+      <c r="K101" s="3">
         <v>-126300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>79700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>157300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>111600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>39900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>8600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>83400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-39400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>51700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-35300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-58100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-69800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>49100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>10000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-82800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>24000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>42100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>41400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>141000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-42500</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>8</v>
+      <c r="D102" s="3">
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>995500</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>-64900</v>
+        <v>927000</v>
       </c>
       <c r="G102" s="3">
-        <v>-2220000</v>
+        <v>-64800</v>
       </c>
       <c r="H102" s="3">
-        <v>-4128900</v>
+        <v>-41800</v>
       </c>
       <c r="I102" s="3">
-        <v>2129200</v>
+        <v>-2119500</v>
       </c>
       <c r="J102" s="3">
+        <v>2255900</v>
+      </c>
+      <c r="K102" s="3">
         <v>149100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>325600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-652600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>402700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-898100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>186600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>414800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-379100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1277400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>989800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>383500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1010300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-809300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-306900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1289300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-496100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>759200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-670400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-710700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>798800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>424100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-166800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1487500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>874100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-181900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1061400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>IX</t>
   </si>
@@ -656,450 +656,462 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4775800</v>
+      </c>
+      <c r="E8" s="3">
         <v>4854600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4402000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5133700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4810700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4572700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4682200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5031200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4473200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4510700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4433700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4331000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4304600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4561900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4474800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4445500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4258400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4261900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4586100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5250300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5208200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5394500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5023800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6138000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5042300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6113700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5489600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6037700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6120900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6558500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7162400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6678100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6250200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5616300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2881500</v>
+      </c>
+      <c r="E9" s="3">
         <v>2662700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2583600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3049700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2692600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2673800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2768100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2887700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2456800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2983700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2816500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2792900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2639600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2863300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2678900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2911600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2651900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2623600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2965900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3323400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3188900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3275300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2984300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3960200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3109200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3952000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3459500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4148400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4173600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4727200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5316600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4878500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4517300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3914700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1894300</v>
+      </c>
+      <c r="E10" s="3">
         <v>2191900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1818400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2084000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2118100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1898900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1914100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2143500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2016400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1527000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1617200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1538100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1665000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1698700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1795800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1534000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1606500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1638300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1620200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1926900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2019300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2119200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2039500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2177800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1933100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2161700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2030100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1889300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1947200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1831300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1845700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1799600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1732900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1701600</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1136,8 +1148,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1253,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1344,216 +1360,225 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-78200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-32900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-162000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-395200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-53900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-14900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-5900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-38100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>136800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>102900</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>13000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-35000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>22500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>4700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>23000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>22600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>14100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>9800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>38400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>30100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>579200</v>
+      </c>
+      <c r="E15" s="3">
         <v>700800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>566100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>599700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>674200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>623400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>590600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>669700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>15700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>13900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>15400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>16000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>14800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>17500</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>15100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>16500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>16700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>20100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>17200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>16400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>16200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>13200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>12500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>10500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>9900</v>
-      </c>
-      <c r="AD15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG15" s="3">
         <v>11400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>11000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>13300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1587,216 +1612,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3556900</v>
+      </c>
+      <c r="E17" s="3">
         <v>4204000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3585500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4070400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3858000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3697900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3860600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3656800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3834400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4082800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3868600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4198400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3801700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3790900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3725200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3979600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3717000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3682900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4160600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4960500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4524800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4603700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4330800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5453200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4446700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5155900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4653400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5469000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5359200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5681200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6330900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5953800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5529800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4916200</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1218900</v>
+      </c>
+      <c r="E18" s="3">
         <v>650600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>816600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1063400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>952700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>874700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>821600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1374400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>638800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>427900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>565100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>132600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>502900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>771000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>749500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>465900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>541400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>579000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>425500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>289800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>683400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>790800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>693000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>684800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>595600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>957800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>836200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>568700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>761700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>877300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>831500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>724300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>720400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>700100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1833,243 +1865,250 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>235300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-541700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-48200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>73000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-222800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-67000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-88700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>320600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>212500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>86100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1117000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>155900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>99500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-14100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>87000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>11300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-60600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>151400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>257300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>426400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>401800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>212600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>281600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>105100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>64000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>172300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>109400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>213500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>180400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>394400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>81700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>298400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1562700</v>
+      </c>
+      <c r="E21" s="3">
         <v>1893100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1430900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1590000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1849600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1565100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1501000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1723600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1512500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1056900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1130600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1804400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1225900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1465700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1335800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1121400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1144900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1126200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1233300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1255100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1783600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1888900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1584500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1712100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1406800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1694300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1652200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1376200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1600300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1668200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1822700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1389400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1580800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1445600</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>257800</v>
+      </c>
+      <c r="E22" s="3">
         <v>270200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>279800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>327900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>338700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>320100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>298000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>293400</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -2145,216 +2184,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>803900</v>
+      </c>
+      <c r="E23" s="3">
         <v>955000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>747000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1057600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>890600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>636500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>618300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>798500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>851300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>514000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>576700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1249600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>658800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>870500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>735400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>552900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>552700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>518400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>576900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>547100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1109900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1192600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>905600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>966400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>700700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1021800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1008600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>678100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>975200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1057700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1225900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>806000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>894100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>234200</v>
+      </c>
+      <c r="E24" s="3">
         <v>278200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>217600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>257900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>273500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>191400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>174500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>198700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>204900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>119700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>143000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>574000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>226000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>278400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>216500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>179500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>187500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>167500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>146500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>86600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>325100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>349300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>265200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>120600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-77300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>310300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>281100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>135400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>142100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>348400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>403800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>300000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>336300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>295100</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2457,216 +2505,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>569700</v>
+      </c>
+      <c r="E26" s="3">
         <v>676800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>529400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>799700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>617100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>445100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>443700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>599900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>646400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>394200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>433700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>675600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>432900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>592100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>518900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>373300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>365200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>350800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>430400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>460500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>784800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>843300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>640300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>845800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>777900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>711500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>727500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>542700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>833100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>709300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>822100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>506000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>682500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>599000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>565100</v>
+      </c>
+      <c r="E27" s="3">
         <v>671500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>539200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>839200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>646300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>436100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>435500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>589900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>636200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>385300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>417400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>668300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>444200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>587400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>479300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>365300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>353100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>341200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>426900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>455800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>775900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>826500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>634000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>841200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>766100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>697700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>726700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>513000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>817400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>689400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>811000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>497800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>665000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2769,8 +2826,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2795,8 +2855,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -2804,11 +2864,11 @@
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3">
         <v>900</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
@@ -2816,11 +2876,11 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
         <v>-8200</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2828,11 +2888,11 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
         <v>58500</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2846,14 +2906,14 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2864,8 +2924,8 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI29" s="3">
         <v>0</v>
@@ -2873,8 +2933,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2977,8 +3040,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3081,216 +3147,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-235300</v>
+      </c>
+      <c r="E32" s="3">
         <v>541700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>48200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-73000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>222800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>67000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>88700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-320600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-212500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-86100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1117000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-155900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-99500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>14100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-87000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-11300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>60600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-151400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-257300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-426400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-401800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-212600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-281600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-105100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-64000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-172300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-109400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-213500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-180400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-394400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-81700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-298400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-194000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>565000</v>
+      </c>
+      <c r="E33" s="3">
         <v>671600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>539200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>839200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>646300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>436100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>435500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>589900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>636200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>385300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>417400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>669300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>444200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>587400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>479300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>357100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>353100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>341200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>426900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>514300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>775900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>826500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>634000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>841200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>766100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>697700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>726700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>513000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>817400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>689400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>811000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>497800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>665000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3393,221 +3468,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>565000</v>
+      </c>
+      <c r="E35" s="3">
         <v>671600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>539200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>839200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>646300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>436100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>435500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>589900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>636200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>385300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>417400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>669300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>444200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>587400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>479300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>357100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>353100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>341200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>426900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>514300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>775900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>826500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>634000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>841200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>766100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>697700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>726700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>513000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>817400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>689400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>811000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>497800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>665000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3644,8 +3728,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3682,139 +3767,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7108700</v>
+      </c>
+      <c r="E41" s="3">
         <v>8159400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6171300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6828300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6415100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6126800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6378400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9266700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7575800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6673600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6706200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7249600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7084100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8377200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8349700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7654200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8305200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10183900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10067500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10001900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9297700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10195800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10468300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12335200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>12604300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11656800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12061800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12702300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11964900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>11518800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>11731700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>10051600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>9284500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>9275800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>126600</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>139000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>198100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>226300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>213000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>220800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3890,243 +3979,252 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>35487900</v>
+      </c>
+      <c r="E43" s="3">
         <v>37039000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>33602900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>36547700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>38203900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>36401600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>37888900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>40837100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2136000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1849700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2251200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1928900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1578100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1519400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1779900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1952500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1566800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1312300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1704500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2254500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1999500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1879200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2136800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2139000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1930100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2040800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2255700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2170500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2281800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1973500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1850500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1988700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1868400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1833400</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1447900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1514100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1351500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1503200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1640100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1492400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1175900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1271500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1036000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>986100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>987100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>926700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>948200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>958100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1006200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1007900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1080000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1053500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1105000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1110200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1202100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1161000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1146700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1111800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1369000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1220500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1117200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1003400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1246700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1174100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1116500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1045400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1265400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1328700</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>341300</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>357000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>384100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>495400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>708000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>373100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4202,35 +4300,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>44886800</v>
+      </c>
+      <c r="E46" s="3">
         <v>48120300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>42144800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>46383400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>47840200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>45673900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>47320300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>52985100</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4306,251 +4407,260 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>29929300</v>
+      </c>
+      <c r="E47" s="3">
         <v>30723000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28805900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>29193900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>30071400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>27829000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>28075100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28293500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>55010700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>51027800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>53430500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>51081400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>52315800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>52503500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>52973200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>51182600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>51463300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>53541500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>58386100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>59973800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>74441200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>71989200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>69844300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>82078400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>78817700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>75266400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>69855700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>69467000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>71014900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>70684000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>70420000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>69927900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>70281800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>67221000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5913100</v>
+      </c>
+      <c r="E48" s="3">
         <v>6569600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5910300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6779200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6461400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5943500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6094500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7319900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16212000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14530600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15370200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15042700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15489200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16390700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15748800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15218300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16071400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16625000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18395500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19086100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6587600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6033700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6371700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5285700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5647800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5234600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5009900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4951600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4682600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4655100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4632500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4521200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4311900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4267300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>8517000</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>8227500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8927300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8608000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8806500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9163100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6633600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6103600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6015300</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>8</v>
@@ -4564,8 +4674,8 @@
       <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -4618,8 +4728,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4722,8 +4835,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4826,35 +4942,38 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26871800</v>
+      </c>
+      <c r="E52" s="3">
         <v>20125100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25723600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16887500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16449000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15698900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15455000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16890000</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -4930,8 +5049,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5034,112 +5156,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>107601000</v>
+      </c>
+      <c r="E54" s="3">
         <v>114055000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>102584500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>107911100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>111868400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>105751300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>107785400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>115014900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>103332600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>94334700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>98555600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>94757300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>96806300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>99748000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>99827500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>96162300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>97668500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>102579300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>111679100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>115124900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>116999300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>114976800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>113629300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>117001000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>114429700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>109422700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>103370600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>103290900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>104429300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>103291400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>102314200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>99626900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>98834300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>95642500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5176,8 +5304,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5214,347 +5343,357 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1897900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2075400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2008500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2396600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2345000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2208300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2178600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2759600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1794600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1585600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1774500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1935000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1556000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1660300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1546400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1848400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1558500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1535100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1627400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2490800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2067100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2140100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2032100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2820300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2206000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2131700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2416200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2371200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1898700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1915700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1891500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2233500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1846800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1846700</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4693500</v>
+      </c>
+      <c r="E58" s="3">
         <v>5220900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3991300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9984300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4615500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3947200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4005700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3852400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3163300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2945500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3984500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2919200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4574600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3561600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3355000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2178500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2722800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2816300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3217100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2967500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3499400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2525500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3084300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2974800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6124400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3014300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2165000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2773100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3241500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3034400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3398100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2514400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2628100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1852200</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3657300</v>
+      </c>
+      <c r="E59" s="3">
         <v>4414400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3381700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7861700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4082900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3918700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4363600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>701400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18750000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16383500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17574500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20002500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18559000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19455100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19718700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21080400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19858200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>20846200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>22491300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>22800700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>23138900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>22619100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21575000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>21945200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>21264700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>21021000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>19682100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>19204700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>19329900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>19044800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>18495000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>18275000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>17244500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>16647500</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10248700</v>
+      </c>
+      <c r="E60" s="3">
         <v>11710800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9381600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20242600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11043400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10074300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10547800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7313500</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5630,139 +5769,145 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36685500</v>
+      </c>
+      <c r="E61" s="3">
         <v>38353200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>35703700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>32754200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37838000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>36476800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36489700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>41356500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>33794000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31572800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>31785500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>29446700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>29889600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>31374300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>31744800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31339600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>31786500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>33212400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>37004500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>37701100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>37525700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>37410700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>37668500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>40229600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>37481900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>35869000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>34202200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>34591600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>35174700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>34962700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>35088200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>34193700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>34384900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>33751200</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>34121300</v>
+      </c>
+      <c r="E62" s="3">
         <v>35953600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31643700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24633400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>35752500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>33269900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>34787700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>35535300</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5838,8 +5983,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5942,8 +6090,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6046,8 +6197,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6150,112 +6304,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>81055500</v>
+      </c>
+      <c r="E66" s="3">
         <v>86264300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>76729000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>81303000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>84862100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>80016200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>82031300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>87818900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>80219200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>72994800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>76355800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>73101400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>75179800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>77269700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>77428100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>74690500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>76131100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>79367500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>86642100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>88751200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>89592700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>87755300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>87183700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>89160100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>87832500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>83373800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>78716600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>79041800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>80311500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>79690300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>79485200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>77383600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>77218100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>74665300</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6292,8 +6452,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6396,8 +6557,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6500,8 +6664,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6604,8 +6771,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6708,112 +6878,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>21598800</v>
+      </c>
+      <c r="E72" s="3">
         <v>23579600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20401500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>21551200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>22515000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20971500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21213900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>22977200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21402300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18983000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19650300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19317900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19625900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20469500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20268200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19459100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>20219500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>21453300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>23117700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>24266800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>24561300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>24406600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>23503000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>24559200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>23318000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>22550800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>21382600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>20930200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>20440400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19935700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19246400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>18427200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>17917900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>17520500</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6916,8 +7092,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7020,8 +7199,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7124,112 +7306,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25991300</v>
+      </c>
+      <c r="E76" s="3">
         <v>27237800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25323200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26058400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>26442600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>25181100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>25198400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26656900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23113400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21339900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22199700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21655800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21626500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22478300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22399400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21471800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21537500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23211700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>25037000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>26373700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>27406600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>27221500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>26445600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>27840900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>26597200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>26048900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24653900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>24249100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>24117900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>23601100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>22829000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>22243300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>21616300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>20977200</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7332,221 +7520,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>565000</v>
+      </c>
+      <c r="E81" s="3">
         <v>671600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>539200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>839200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>646300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>436100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>435500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>589900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>636200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>385300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>417400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>669300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>444200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>587400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>479300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>357100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>353100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>341200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>426900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>514300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>775900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>826500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>634000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>841200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>766100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>697700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>726700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>513000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>817400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>689400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>811000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>497800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>665000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7583,112 +7780,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>674200</v>
+      </c>
+      <c r="E83" s="3">
         <v>623400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>590600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>412400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>687800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>561400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>583400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>688200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>661200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>543000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>553900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>554900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>567100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>595200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>600400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>568500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>592200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>607800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>656400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>708000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>673700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>696300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>678900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>745700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>706100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>672500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>643600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>698100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>625100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>610500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>596800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>583400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>562000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>551500</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7791,8 +7992,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7895,8 +8099,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7999,8 +8206,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8103,8 +8313,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8207,8 +8420,11 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8218,101 +8434,104 @@
       <c r="E89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>2094600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2380500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2638800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1361800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2508500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2248700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1879900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-214000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2243300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1184200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2698700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1608600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2407900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1732000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2631100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1552600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2834900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1711200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3255200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1636300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1980300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1020200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1637600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>884100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1772000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1193700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1172300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>803500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1250000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>994000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1888000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8349,8 +8568,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8360,101 +8580,104 @@
       <c r="E91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1657000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2075200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2252700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2221800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2280700</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-254596000</v>
       </c>
       <c r="L91" s="3">
         <v>-254596000</v>
       </c>
       <c r="M91" s="3">
+        <v>-254596000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-223427000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-248094000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-229768000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-256101000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-39500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-42700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-84600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-133300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-79200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-172200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-116600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-62600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-48600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-106500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-127700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-198600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-147500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-155900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-197500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-222200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2642900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2149200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2170900</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8557,8 +8780,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8661,8 +8887,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8672,101 +8901,104 @@
       <c r="E94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1041600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2521100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3014300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2833300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3059900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1783200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1362800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1529700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-236300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2314500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2310200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-852200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2514400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3140600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1425100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2023400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3372700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3499800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3389900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3065100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1698000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3863100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2709000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>32500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-760600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1359900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>116900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1077700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1208800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-357200</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8803,8 +9035,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8814,101 +9047,104 @@
       <c r="E96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>352500</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>347300</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-359200</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-375400</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-322600</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-385400</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-320100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-439200</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-408700</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-540100</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-363000</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-454400</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-312700</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-345000</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-267500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9011,8 +9247,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9115,8 +9354,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9219,8 +9461,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9230,205 +9475,211 @@
       <c r="E100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>-217400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>128100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>286700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-784900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2776100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-190100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-271200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>933800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1715900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>192400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-205900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-350200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-356000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>131600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-216700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>852700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1587500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>927700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-136900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>197600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-769700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3671900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>352000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1637300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-330300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>571200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>434300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>622800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>713600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-108100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-426900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-52300</v>
+      </c>
+      <c r="E101" s="3">
         <v>47100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>136900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>31200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-134900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>86300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>171700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>138400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-126300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>79700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>157300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>111600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>39900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>8600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>83400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-39400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>51700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-35300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-58100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-69800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>49100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>10000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-82800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>24000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>42100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>41400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>141000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-42500</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9439,96 +9690,99 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>927000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-64800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-41800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2119500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2255900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>149100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>325600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-652600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>402700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-898100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>186600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>414800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-379100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1277400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>989800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>383500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1010300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-809300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-306900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1289300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-496100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>759200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-670400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-710700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>798800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>424100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-166800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1487500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>874100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-181900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1061400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>IX</t>
   </si>
@@ -656,462 +656,474 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4810300</v>
+      </c>
+      <c r="E8" s="3">
         <v>4775800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4854600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4402000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5133700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4810700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4572700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4682200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5031200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4473200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4510700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4433700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4331000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4304600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4561900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4474800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4445500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4258400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4261900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4586100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5250300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5208200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5394500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5023800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6138000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5042300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6113700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5489600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6037700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6120900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6558500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7162400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6678100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6250200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5616300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2832500</v>
+      </c>
+      <c r="E9" s="3">
         <v>2881500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2662700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2583600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3049700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2692600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2673800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2768100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2887700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2456800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2983700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2816500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2792900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2639600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2863300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2678900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2911600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2651900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2623600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2965900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3323400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3188900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3275300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2984300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3960200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3109200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3952000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3459500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4148400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4173600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4727200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5316600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4878500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4517300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3914700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1977900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1894300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2191900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1818400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2084000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2118100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1898900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1914100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2143500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2016400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1527000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1617200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1538100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1665000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1698700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1795800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1534000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1606500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1638300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1620200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1926900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2019300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2119200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2039500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2177800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1933100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2161700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2030100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1889300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1947200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1831300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1845700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1799600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1732900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1701600</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1149,8 +1161,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1256,8 +1269,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1363,222 +1379,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-146300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-78200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-32900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-162000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-395200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-53900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-14900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-38100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>136800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>102900</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>13000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-35000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>22500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>23000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>22600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>14100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>3500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>9800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>38400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>30100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>667000</v>
+      </c>
+      <c r="E15" s="3">
         <v>579200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>700800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>566100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>599700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>674200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>623400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>590600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>669700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>15700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>13900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>14600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>15400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>16000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>14800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>17500</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="T15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>15100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>16500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>16700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>20100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>17200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>16400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>16200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>13200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>12500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>10500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>9900</v>
-      </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH15" s="3">
         <v>11400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>11000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>13300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>11900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1613,222 +1638,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4068000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3556900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4204000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3585500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4070400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3858000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3697900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3860600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3656800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3834400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4082800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3868600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4198400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3801700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3790900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3725200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3979600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3717000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3682900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4160600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4960500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4524800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4603700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4330800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5453200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4446700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5155900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4653400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5469000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5359200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5681200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6330900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5953800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5529800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4916200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>742300</v>
+      </c>
+      <c r="E18" s="3">
         <v>1218900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>650600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>816600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1063400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>952700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>874700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>821600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1374400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>638800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>427900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>565100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>132600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>502900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>771000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>749500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>465900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>541400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>579000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>425500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>289800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>683400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>790800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>693000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>684800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>595600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>957800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>836200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>568700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>761700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>877300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>831500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>724300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>720400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>700100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1866,252 +1898,259 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-58900</v>
+      </c>
+      <c r="E20" s="3">
         <v>235300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-541700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-48200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>73000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-222800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-67000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-88700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>320600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>212500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>86100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>11600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1117000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>155900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>99500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-14100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>87000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>11300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-60600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>151400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>257300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>426400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>401800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>212600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>281600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>105100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>64000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>172300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>109400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>213500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>180400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>394400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>81700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>298400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1468200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1562700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1893100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1430900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1590000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1849600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1565100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1501000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1723600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1512500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1056900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1130600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1804400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1225900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1465700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1335800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1121400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1144900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1126200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1233300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1255100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1783600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1888900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1584500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1712100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1406800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1694300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1652200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1376200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1600300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1668200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1822700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1389400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1580800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1445600</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>299100</v>
+      </c>
+      <c r="E22" s="3">
         <v>257800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>270200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>279800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>327900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>338700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>320100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>298000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>293400</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -2187,222 +2226,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>648300</v>
+      </c>
+      <c r="E23" s="3">
         <v>803900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>955000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>747000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1057600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>890600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>636500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>618300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>798500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>851300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>514000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>576700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1249600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>658800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>870500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>735400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>552900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>552700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>518400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>576900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>547100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1109900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1192600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>905600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>966400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>700700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1021800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1008600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>678100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>975200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1057700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1225900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>806000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>894100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>114500</v>
+      </c>
+      <c r="E24" s="3">
         <v>234200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>278200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>217600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>257900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>273500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>191400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>174500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>198700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>204900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>119700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>143000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>574000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>226000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>278400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>216500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>179500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>187500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>167500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>146500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>86600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>325100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>349300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>265200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>120600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-77300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>310300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>281100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>135400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>142100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>348400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>403800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>300000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>336300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>295100</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2508,222 +2556,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>533800</v>
+      </c>
+      <c r="E26" s="3">
         <v>569700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>676800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>529400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>799700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>617100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>445100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>443700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>599900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>646400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>394200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>433700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>675600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>432900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>592100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>518900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>373300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>365200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>350800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>430400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>460500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>784800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>843300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>640300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>845800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>777900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>711500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>727500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>542700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>833100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>709300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>822100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>506000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>682500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>599000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>533200</v>
+      </c>
+      <c r="E27" s="3">
         <v>565100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>671500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>539200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>839200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>646300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>436100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>435500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>589900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>636200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>385300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>417400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>668300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>444200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>587400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>479300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>365300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>353100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>341200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>426900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>455800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>775900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>826500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>634000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>841200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>766100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>697700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>726700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>513000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>817400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>689400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>811000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>497800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>665000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2829,8 +2886,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2858,8 +2918,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -2867,11 +2927,11 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3">
         <v>900</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
@@ -2879,11 +2939,11 @@
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3">
         <v>-8200</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2891,11 +2951,11 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>58500</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2909,14 +2969,14 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2927,8 +2987,8 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ29" s="3">
         <v>0</v>
@@ -2936,8 +2996,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3043,8 +3106,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3150,222 +3216,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-235300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>541700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>48200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-73000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>222800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>67000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>88700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-320600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-212500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-86100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-11600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1117000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-155900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-99500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>14100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-87000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-11300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>60600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-151400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-257300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-426400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-401800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-212600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-281600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-105100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-64000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-172300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-109400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-213500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-180400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-394400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-81700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-298400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-194000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>533200</v>
+      </c>
+      <c r="E33" s="3">
         <v>565000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>671600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>539200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>839200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>646300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>436100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>435500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>589900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>636200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>385300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>417400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>669300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>444200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>587400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>479300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>357100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>353100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>341200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>426900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>514300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>775900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>826500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>634000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>841200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>766100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>697700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>726700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>513000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>817400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>689400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>811000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>497800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>665000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3471,227 +3546,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>533200</v>
+      </c>
+      <c r="E35" s="3">
         <v>565000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>671600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>539200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>839200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>646300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>436100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>435500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>589900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>636200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>385300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>417400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>669300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>444200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>587400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>479300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>357100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>353100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>341200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>426900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>514300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>775900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>826500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>634000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>841200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>766100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>697700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>726700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>513000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>817400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>689400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>811000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>497800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>665000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3729,8 +3813,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3768,115 +3853,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5611800</v>
+      </c>
+      <c r="E41" s="3">
         <v>7108700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8159400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6171300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6828300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6415100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6126800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6378400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9266700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7575800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6673600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6706200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7249600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7084100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8377200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8349700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7654200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8305200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10183900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10067500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10001900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9297700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10195800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10468300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>12335200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12604300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11656800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12061800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12702300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>11964900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>11518800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>11731700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>10051600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>9284500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>9275800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3884,29 +3973,29 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>126600</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>139000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>198100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>226300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>213000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>220800</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3982,252 +4071,261 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>34669100</v>
+      </c>
+      <c r="E43" s="3">
         <v>35487900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>37039000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>33602900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>36547700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>38203900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>36401600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>37888900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>40837100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2136000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1849700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2251200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1928900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1578100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1519400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1779900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1952500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1566800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1312300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1704500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2254500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1999500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1879200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2136800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2139000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1930100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2040800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2255700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2170500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2281800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1973500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1850500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1988700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1868400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1833400</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1530800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1447900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1514100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1351500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1503200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1640100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1492400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1175900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1271500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1036000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>986100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>987100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>926700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>948200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>958100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1006200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1007900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1080000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1053500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1105000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1110200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1202100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1161000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1146700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1111800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1369000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1220500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1117200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1003400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1246700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1174100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1116500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1045400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1265400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1328700</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>341300</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>357000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>384100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>495400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>708000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>373100</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4303,38 +4401,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>41811700</v>
+      </c>
+      <c r="E46" s="3">
         <v>44886800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>48120300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>42144800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>46383400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>47840200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>45673900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>47320300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>52985100</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4410,222 +4511,231 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>30414800</v>
+      </c>
+      <c r="E47" s="3">
         <v>29929300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>30723000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28805900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>29193900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>30071400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>27829000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28075100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28293500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>55010700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>51027800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>53430500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>51081400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>52315800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>52503500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>52973200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>51182600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>51463300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>53541500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>58386100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>59973800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>74441200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>71989200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>69844300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>82078400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>78817700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>75266400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>69855700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>69467000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>71014900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>70684000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>70420000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>69927900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>70281800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>67221000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5154300</v>
+      </c>
+      <c r="E48" s="3">
         <v>5913100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6569600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5910300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6779200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6461400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5943500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6094500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7319900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16212000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14530600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15370200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15042700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15489200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16390700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15748800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15218300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16071400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16625000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18395500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19086100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6587600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6033700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6371700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5285700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5647800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5234600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5009900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4951600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4682600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4655100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4632500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4521200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4311900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4267300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4633,37 +4743,37 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>8517000</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>8227500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8927300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8608000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8806500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9163100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6633600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6103600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6015300</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>8</v>
@@ -4677,8 +4787,8 @@
       <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -4731,8 +4841,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4838,8 +4951,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4945,38 +5061,41 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>35250000</v>
+      </c>
+      <c r="E52" s="3">
         <v>26871800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20125100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25723600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16887500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16449000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15698900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15455000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16890000</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -5052,8 +5171,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5159,115 +5281,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>112630900</v>
+      </c>
+      <c r="E54" s="3">
         <v>107601000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>114055000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>102584500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>107911100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>111868400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>105751300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>107785400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>115014900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>103332600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>94334700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>98555600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>94757300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>96806300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>99748000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>99827500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>96162300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>97668500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>102579300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>111679100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>115124900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>116999300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>114976800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>113629300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>117001000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>114429700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>109422700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>103370600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>103290900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>104429300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>103291400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>102314200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>99626900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>98834300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>95642500</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5305,8 +5433,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5344,359 +5473,369 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>1897900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2075400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2008500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2396600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2345000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2208300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2178600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2759600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1794600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1585600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1774500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1935000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1556000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1660300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1546400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1848400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1558500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1535100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1627400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2490800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2067100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2140100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2032100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2820300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2206000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2131700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2416200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2371200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1898700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1915700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1891500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2233500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1846800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1846700</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3670700</v>
+      </c>
+      <c r="E58" s="3">
         <v>4693500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5220900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3991300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9984300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4615500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3947200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4005700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3852400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3163300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2945500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3984500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2919200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4574600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3561600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3355000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2178500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2722800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2816300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3217100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2967500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3499400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2525500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3084300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2974800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6124400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3014300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2165000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2773100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3241500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3034400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3398100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2514400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2628100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1852200</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>3657300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4414400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3381700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7861700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4082900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3918700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4363600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>701400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18750000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16383500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17574500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20002500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18559000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19455100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19718700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>21080400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>19858200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>20846200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>22491300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>22800700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>23138900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>22619100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>21575000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>21945200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>21264700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>21021000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>19682100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>19204700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>19329900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>19044800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>18495000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>18275000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>17244500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>16647500</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3670700</v>
+      </c>
+      <c r="E60" s="3">
         <v>10248700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11710800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9381600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20242600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11043400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10074300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10547800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7313500</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5772,145 +5911,151 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>38285100</v>
+      </c>
+      <c r="E61" s="3">
         <v>36685500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>38353200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>35703700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>32754200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37838000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36476800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>36489700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>41356500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>33794000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>31572800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>31785500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>29446700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>29889600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>31374300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31744800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>31339600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>31786500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>33212400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>37004500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>37701100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>37525700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>37410700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>37668500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>40229600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>37481900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>35869000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>34202200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>34591600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>35174700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>34962700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>35088200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>34193700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>34384900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>33751200</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>42793500</v>
+      </c>
+      <c r="E62" s="3">
         <v>34121300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>35953600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>31643700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24633400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>35752500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>33269900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>34787700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>35535300</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5986,8 +6131,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6093,8 +6241,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6200,8 +6351,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6307,115 +6461,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>84749300</v>
+      </c>
+      <c r="E66" s="3">
         <v>81055500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>86264300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>76729000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>81303000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>84862100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>80016200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>82031300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>87818900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>80219200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>72994800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>76355800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>73101400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>75179800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>77269700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>77428100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>74690500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>76131100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>79367500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>86642100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>88751200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>89592700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>87755300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>87183700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>89160100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>87832500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>83373800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>78716600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>79041800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>80311500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>79690300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>79485200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>77383600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>77218100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>74665300</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6453,8 +6613,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6560,8 +6721,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6667,8 +6831,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6774,8 +6941,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6881,115 +7051,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>21598800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>23579600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20401500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21551200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>22515000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20971500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21213900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22977200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21402300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18983000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19650300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19317900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19625900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20469500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>20268200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19459100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20219500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>21453300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>23117700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>24266800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>24561300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>24406600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>23503000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>24559200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>23318000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>22550800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>21382600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>20930200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>20440400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19935700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>19246400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>18427200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>17917900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>17520500</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7095,8 +7271,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7202,8 +7381,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7309,115 +7491,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27311100</v>
+      </c>
+      <c r="E76" s="3">
         <v>25991300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>27237800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25323200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>26058400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>26442600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>25181100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25198400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26656900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23113400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21339900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22199700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21655800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21626500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22478300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22399400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21471800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21537500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>23211700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>25037000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>26373700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>27406600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>27221500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>26445600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>27840900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>26597200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>26048900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>24653900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>24249100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>24117900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>23601100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>22829000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>22243300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>21616300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>20977200</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7523,227 +7711,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>533200</v>
+      </c>
+      <c r="E81" s="3">
         <v>565000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>671600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>539200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>839200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>646300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>436100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>435500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>589900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>636200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>385300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>417400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>669300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>444200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>587400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>479300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>357100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>353100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>341200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>426900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>514300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>775900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>826500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>634000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>841200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>766100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>697700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>726700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>513000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>817400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>689400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>811000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>497800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>665000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7781,115 +7978,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>340400</v>
+      </c>
+      <c r="E83" s="3">
         <v>674200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>623400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>590600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>412400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>687800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>561400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>583400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>688200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>661200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>543000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>553900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>554900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>567100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>595200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>600400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>568500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>592200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>607800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>656400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>708000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>673700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>696300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>678900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>745700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>706100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>672500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>643600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>698100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>625100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>610500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>596800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>583400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>562000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>551500</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7995,8 +8196,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8102,8 +8306,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8209,8 +8416,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8316,8 +8526,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8423,8 +8636,11 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8437,101 +8653,104 @@
       <c r="F89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3">
         <v>2094600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2380500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2638800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1361800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2508500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2248700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1879900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-214000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2243300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1184200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2698700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1608600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2407900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1732000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2631100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1552600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2834900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1711200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3255200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1636300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1980300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1020200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1637600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>884100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1772000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1193700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1172300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>803500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1250000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>994000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1888000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8569,8 +8788,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8583,101 +8803,104 @@
       <c r="F91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1657000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2075200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2252700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2221800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2280700</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-254596000</v>
       </c>
       <c r="M91" s="3">
         <v>-254596000</v>
       </c>
       <c r="N91" s="3">
+        <v>-254596000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-223427000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-248094000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-229768000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-256101000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-39500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-42700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-84600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-133300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-79200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-172200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-116600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-62600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-48600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-106500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-127700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-198600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-147500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-155900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-197500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-222200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2642900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2149200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2170900</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8783,8 +9006,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8890,8 +9116,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8904,101 +9133,104 @@
       <c r="F94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1041600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2521100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3014300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2833300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3059900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1783200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1362800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1529700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-236300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2314500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2310200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-852200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2514400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3140600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1425100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2023400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3372700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3499800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3389900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3065100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1698000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3863100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2709000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>32500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-760600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1359900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>116900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1077700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1208800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-357200</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9036,8 +9268,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9050,101 +9283,104 @@
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>352500</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>347300</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-359200</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-375400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-322600</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-385400</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-320100</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-439200</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-408700</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-540100</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-363000</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-454400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-312700</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-345000</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-267500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9250,8 +9486,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9357,8 +9596,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9464,8 +9706,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9478,208 +9723,214 @@
       <c r="F100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3">
         <v>-217400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>128100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>286700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-784900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2776100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-190100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-271200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>933800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1715900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>192400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-205900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-350200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-356000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>131600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-216700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>852700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1587500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>927700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-136900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>197600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-769700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3671900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>352000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1637300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-330300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>571200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>434300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>622800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>713600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-108100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-426900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-52300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>47100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>136900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>31200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-134900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>86300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>171700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>138400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-126300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>79700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>157300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>111600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>39900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>8600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>83400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-39400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>51700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-35300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-58100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-69800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>49100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>10000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-82800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>24000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>42100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>41400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>141000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-42500</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9693,96 +9944,99 @@
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>927000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-64800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-41800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2119500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2255900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>149100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>325600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-652600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>402700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-898100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>186600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>414800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-379100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1277400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>989800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>383500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1010300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-809300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-306900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1289300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-496100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>759200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-670400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-710700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>798800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>424100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-166800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1487500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>874100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-181900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1061400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
   <si>
     <t>IX</t>
   </si>
@@ -656,474 +656,491 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
         <v>4810300</v>
       </c>
-      <c r="E8" s="3">
-        <v>4775800</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3">
         <v>4854600</v>
       </c>
-      <c r="G8" s="3">
-        <v>4402000</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3">
         <v>5133700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4810700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4572700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4682200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5031200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4473200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4510700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4433700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4331000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4304600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4561900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4474800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4445500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4258400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4261900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4586100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5250300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5208200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5394500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5023800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6138000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5042300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6113700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5489600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6037700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6120900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6558500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7162400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6678100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6250200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5616300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
         <v>2832500</v>
       </c>
-      <c r="E9" s="3">
-        <v>2881500</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3">
         <v>2662700</v>
       </c>
-      <c r="G9" s="3">
-        <v>2583600</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3">
         <v>3049700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2692600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2673800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2768100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2887700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2456800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2983700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2816500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2792900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2639600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2863300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2678900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2911600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2651900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2623600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2965900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3323400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3188900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3275300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2984300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3960200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3109200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3952000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3459500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4148400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4173600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4727200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>5316600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4878500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4517300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3914700</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
         <v>1977900</v>
       </c>
-      <c r="E10" s="3">
-        <v>1894300</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3">
         <v>2191900</v>
       </c>
-      <c r="G10" s="3">
-        <v>1818400</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3">
         <v>2084000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2118100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1898900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1914100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2143500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2016400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1527000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1617200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1538100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1665000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1698700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1795800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1534000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1606500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1638300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1620200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1926900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2019300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2119200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2039500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2177800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1933100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2161700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2030100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1889300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1947200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1831300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1845700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1799600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1732900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1701600</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1162,8 +1179,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1272,8 +1290,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1382,228 +1403,237 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>-146300</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>-78200</v>
-      </c>
-      <c r="F14" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-32900</v>
       </c>
-      <c r="G14" s="3">
-        <v>-162000</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>-395200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-53900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-14900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-5900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-38100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>136800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>102900</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>13000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-35000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>22500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>4700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>23000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
         <v>200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>22600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>14100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>3500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>38400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>30100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>667000</v>
       </c>
-      <c r="E15" s="3">
-        <v>579200</v>
-      </c>
       <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
         <v>700800</v>
       </c>
-      <c r="G15" s="3">
-        <v>566100</v>
-      </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>599700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>674200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>623400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>590600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>669700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>15700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>13900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>14600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>15400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>16000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>14800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>17500</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V15" s="3">
         <v>15100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>16500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>16700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>20100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>17200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>16400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>16200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>13200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>12500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>10500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>9900</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AH15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI15" s="3">
         <v>11400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>13300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>11900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1639,228 +1669,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>4068000</v>
+      <c r="D17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E17" s="3">
-        <v>3556900</v>
-      </c>
-      <c r="F17" s="3">
+        <v>3949300</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3">
         <v>4204000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3585500</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3">
         <v>4070400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3858000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3697900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3860600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3656800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3834400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4082800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3868600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4198400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3801700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3790900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3725200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3979600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3717000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3682900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4160600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4960500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4524800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4603700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4330800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5453200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4446700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5155900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4653400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5469000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5359200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5681200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6330900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5953800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5529800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4916200</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>742300</v>
+      <c r="D18" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E18" s="3">
-        <v>1218900</v>
-      </c>
-      <c r="F18" s="3">
+        <v>861000</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3">
         <v>650600</v>
       </c>
-      <c r="G18" s="3">
-        <v>816600</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3">
         <v>1063400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>952700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>874700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>821600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1374400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>638800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>427900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>565100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>132600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>502900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>771000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>749500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>465900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>541400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>579000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>425500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>289800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>683400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>790800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>693000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>684800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>595600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>957800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>836200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>568700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>761700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>877300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>831500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>724300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>720400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>700100</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1899,261 +1936,268 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-58900</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3">
-        <v>235300</v>
-      </c>
-      <c r="F20" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3">
         <v>-541700</v>
       </c>
-      <c r="G20" s="3">
-        <v>-48200</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>73000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-222800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-67000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-88700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>320600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>212500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>86100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>11600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1117000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>155900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>99500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-14100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>87000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>11300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-60600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>151400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>257300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>426400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>401800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>212600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>281600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>105100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>64000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>172300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>109400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>213500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>180400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>394400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>81700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>298400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1468200</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
-        <v>1562700</v>
+        <v>1563400</v>
       </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>1893100</v>
       </c>
-      <c r="G21" s="3">
-        <v>1430900</v>
-      </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>1590000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1849600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1565100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1501000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1723600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1512500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1056900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1130600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1804400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1225900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1465700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1335800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1121400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1144900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1126200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1233300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1255100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1783600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1888900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1584500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1712100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1406800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1694300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1652200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1376200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1600300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1668200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1822700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1389400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1580800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1445600</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>299100</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>257800</v>
-      </c>
-      <c r="F22" s="3">
+        <v>298900</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3">
         <v>270200</v>
       </c>
-      <c r="G22" s="3">
-        <v>279800</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>327900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>338700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>320100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>298000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>293400</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -2229,228 +2273,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
         <v>648300</v>
       </c>
-      <c r="E23" s="3">
-        <v>803900</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3">
         <v>955000</v>
       </c>
-      <c r="G23" s="3">
-        <v>747000</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3">
         <v>1057600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>890600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>636500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>618300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>798500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>851300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>514000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>576700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1249600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>658800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>870500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>735400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>552900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>552700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>518400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>576900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>547100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1109900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1192600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>905600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>966400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>700700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1021800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1008600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>678100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>975200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1057700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1225900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>806000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>894100</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
         <v>114500</v>
       </c>
-      <c r="E24" s="3">
-        <v>234200</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3">
         <v>278200</v>
       </c>
-      <c r="G24" s="3">
-        <v>217600</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3">
         <v>257900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>273500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>191400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>174500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>198700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>204900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>119700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>143000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>574000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>226000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>278400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>216500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>179500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>187500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>167500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>146500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>86600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>325100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>349300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>265200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>120600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-77300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>310300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>281100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>135400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>142100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>348400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>403800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>300000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>336300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>295100</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2559,228 +2612,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
         <v>533800</v>
       </c>
-      <c r="E26" s="3">
-        <v>569700</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3">
         <v>676800</v>
       </c>
-      <c r="G26" s="3">
-        <v>529400</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3">
         <v>799700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>617100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>445100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>443700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>599900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>646400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>394200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>433700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>675600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>432900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>592100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>518900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>373300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>365200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>350800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>430400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>460500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>784800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>843300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>640300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>845800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>777900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>711500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>727500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>542700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>833100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>709300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>822100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>506000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>682500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>599000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>533200</v>
+      <c r="D27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E27" s="3">
-        <v>565100</v>
-      </c>
-      <c r="F27" s="3">
+        <v>533000</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3">
         <v>671500</v>
       </c>
-      <c r="G27" s="3">
-        <v>539200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>839200</v>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I27" s="3">
+        <v>839100</v>
+      </c>
+      <c r="J27" s="3">
         <v>646300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>436100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>435500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>589900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>636200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>385300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>417400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>668300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>444200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>587400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>479300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>365300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>353100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>341200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>426900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>455800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>775900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>826500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>634000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>841200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>766100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>697700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>726700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>513000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>817400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>689400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>811000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>497800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>665000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2889,8 +2951,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2921,8 +2986,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
@@ -2930,36 +2995,36 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3">
         <v>900</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3">
         <v>-8200</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>58500</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2972,14 +3037,14 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2990,8 +3055,8 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK29" s="3">
         <v>0</v>
@@ -2999,8 +3064,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3109,8 +3177,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3219,228 +3290,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>58900</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3">
-        <v>-235300</v>
-      </c>
-      <c r="F32" s="3">
+        <v>35400</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3">
         <v>541700</v>
       </c>
-      <c r="G32" s="3">
-        <v>48200</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>-73000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>222800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>67000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>88700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-320600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-212500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-86100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-11600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1117000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-155900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-99500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>14100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-87000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-11300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>60600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-151400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-257300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-426400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-401800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-212600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-281600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-105100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-64000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-172300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-109400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-213500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-180400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-394400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-81700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-298400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-194000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
         <v>533200</v>
       </c>
-      <c r="E33" s="3">
-        <v>565000</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3">
         <v>671600</v>
       </c>
-      <c r="G33" s="3">
-        <v>539200</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3">
         <v>839200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>646300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>436100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>435500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>589900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>636200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>385300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>417400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>669300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>444200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>587400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>479300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>357100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>353100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>341200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>426900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>514300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>775900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>826500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>634000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>841200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>766100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>697700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>726700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>513000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>817400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>689400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>811000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>497800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>665000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3549,233 +3629,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
         <v>533200</v>
       </c>
-      <c r="E35" s="3">
-        <v>565000</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3">
         <v>671600</v>
       </c>
-      <c r="G35" s="3">
-        <v>539200</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3">
         <v>839200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>646300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>436100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>435500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>589900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>636200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>385300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>417400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>669300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>444200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>587400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>479300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>357100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>353100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>341200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>426900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>514300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>775900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>826500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>634000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>841200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>766100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>697700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>726700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>513000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>817400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>689400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>811000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>497800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>665000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3814,8 +3903,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3854,118 +3944,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>5611800</v>
+      <c r="D41" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E41" s="3">
-        <v>7108700</v>
-      </c>
-      <c r="F41" s="3">
+        <v>8057400</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="3">
         <v>8159400</v>
       </c>
-      <c r="G41" s="3">
-        <v>6171300</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3">
         <v>6828300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6415100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6126800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6378400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9266700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7575800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6673600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6706200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7249600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7084100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8377200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8349700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7654200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8305200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10183900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10067500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10001900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9297700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10195800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10468300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12335200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12604300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11656800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12061800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>12702300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>11964900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>11518800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>11731700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>10051600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>9284500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>9275800</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3973,32 +4067,32 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>128700</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>126600</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>139000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>198100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>226300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>213000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>220800</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4074,261 +4168,270 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>34669100</v>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E43" s="3">
-        <v>35487900</v>
-      </c>
-      <c r="F43" s="3">
+        <v>37921600</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
         <v>37039000</v>
       </c>
-      <c r="G43" s="3">
-        <v>33602900</v>
-      </c>
-      <c r="H43" s="3">
-        <v>36547700</v>
+      <c r="H43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I43" s="3">
+        <v>36640000</v>
+      </c>
+      <c r="J43" s="3">
         <v>38203900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>36401600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>37888900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>40837100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2136000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1849700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2251200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1928900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1578100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1519400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1779900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1952500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1566800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1312300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1704500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2254500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1999500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1879200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2136800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2139000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1930100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2040800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2255700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2170500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2281800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1973500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1850500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1988700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1868400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1833400</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>1530800</v>
       </c>
-      <c r="E44" s="3">
-        <v>1447900</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3">
         <v>1514100</v>
       </c>
-      <c r="G44" s="3">
-        <v>1351500</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3">
         <v>1503200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1640100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1492400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1175900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1271500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1036000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>986100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>987100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>926700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>948200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>958100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1006200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1007900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1080000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1053500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1105000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1110200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1202100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1161000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1146700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1111800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1369000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1220500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1117200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1003400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1246700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1174100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1116500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1045400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1265400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1328700</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="E45" s="3">
+        <v>309200</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>341300</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>357000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>384100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>495400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>708000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>373100</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4404,41 +4507,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>41811700</v>
+      <c r="D46" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E46" s="3">
-        <v>44886800</v>
-      </c>
-      <c r="F46" s="3">
+        <v>48718300</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3">
         <v>48120300</v>
       </c>
-      <c r="G46" s="3">
-        <v>42144800</v>
-      </c>
-      <c r="H46" s="3">
-        <v>46383400</v>
+      <c r="H46" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I46" s="3">
+        <v>46475600</v>
+      </c>
+      <c r="J46" s="3">
         <v>47840200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>45673900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>47320300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>52985100</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4514,270 +4620,279 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>30414800</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3">
-        <v>29929300</v>
-      </c>
-      <c r="F47" s="3">
+        <v>29531300</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>30723000</v>
       </c>
-      <c r="G47" s="3">
-        <v>28805900</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>29193900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>30071400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>27829000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28075100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28293500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>55010700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>51027800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>53430500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>51081400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>52315800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>52503500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>52973200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>51182600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>51463300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>53541500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>58386100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>59973800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>74441200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>71989200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>69844300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>82078400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>78817700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>75266400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>69855700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>69467000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>71014900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>70684000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>70420000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>69927900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>70281800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>67221000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>5154300</v>
+      <c r="D48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E48" s="3">
-        <v>5913100</v>
-      </c>
-      <c r="F48" s="3">
+        <v>6927100</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3">
         <v>6569600</v>
       </c>
-      <c r="G48" s="3">
-        <v>5910300</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3">
         <v>6779200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6461400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5943500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6094500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7319900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16212000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14530600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15370200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15042700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15489200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>16390700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15748800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15218300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16071400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16625000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18395500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19086100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6587600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6033700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6371700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5285700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5647800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5234600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5009900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4951600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4682600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4655100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4632500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4521200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4311900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4267300</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
+        <v>8171900</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="3">
         <v>8517000</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3">
         <v>8227500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8927300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8608000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8806500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9163100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6633600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6103600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6015300</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4790,8 +4905,8 @@
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -4844,8 +4959,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4954,8 +5072,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5064,41 +5185,44 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>35250000</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E52" s="3">
-        <v>26871800</v>
-      </c>
-      <c r="F52" s="3">
+        <v>18859400</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>20125100</v>
       </c>
-      <c r="G52" s="3">
-        <v>25723600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>16887500</v>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I52" s="3">
+        <v>16795200</v>
+      </c>
+      <c r="J52" s="3">
         <v>16449000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15698900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15455000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16890000</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -5174,8 +5298,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5284,118 +5411,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
         <v>112630900</v>
       </c>
-      <c r="E54" s="3">
-        <v>107601000</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="3">
         <v>114055000</v>
       </c>
-      <c r="G54" s="3">
-        <v>102584500</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3">
         <v>107911100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>111868400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>105751300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>107785400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>115014900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>103332600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>94334700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>98555600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>94757300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>96806300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>99748000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>99827500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>96162300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>97668500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>102579300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>111679100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>115124900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>116999300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>114976800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>113629300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>117001000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>114429700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>109422700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>103370600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>103290900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>104429300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>103291400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>102314200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>99626900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>98834300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>95642500</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5434,8 +5567,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5474,8 +5608,9 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5483,219 +5618,225 @@
         <v>8</v>
       </c>
       <c r="E57" s="3">
-        <v>1897900</v>
-      </c>
-      <c r="F57" s="3">
+        <v>2269100</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3">
         <v>2075400</v>
       </c>
-      <c r="G57" s="3">
-        <v>2008500</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
         <v>2396600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2345000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2208300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2178600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2759600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1794600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1585600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1774500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1935000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1556000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1660300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1546400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1848400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1558500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1535100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1627400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2490800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2067100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2140100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2032100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2820300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2206000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2131700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2416200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2371200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1898700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1915700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1891500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2233500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1846800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1846700</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>3670700</v>
+      <c r="D58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E58" s="3">
-        <v>4693500</v>
-      </c>
-      <c r="F58" s="3">
+        <v>9838800</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3">
         <v>5220900</v>
       </c>
-      <c r="G58" s="3">
-        <v>3991300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>9984300</v>
+      <c r="H58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I58" s="3">
+        <v>3820200</v>
+      </c>
+      <c r="J58" s="3">
         <v>4615500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3947200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4005700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3852400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3163300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2945500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3984500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2919200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4574600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3561600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3355000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2178500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2722800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2816300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3217100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2967500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3499400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2525500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3084300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2974800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>6124400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3014300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2165000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2773100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3241500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3034400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3398100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2514400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2628100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1852200</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5703,142 +5844,145 @@
         <v>8</v>
       </c>
       <c r="E59" s="3">
-        <v>3657300</v>
-      </c>
-      <c r="F59" s="3">
+        <v>10444200</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>4414400</v>
       </c>
-      <c r="G59" s="3">
-        <v>3381700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>7861700</v>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I59" s="3">
+        <v>1041200</v>
+      </c>
+      <c r="J59" s="3">
         <v>4082900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3918700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4363600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>701400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18750000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16383500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17574500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20002500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18559000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19455100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19718700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21080400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>19858200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>20846200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>22491300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>22800700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>23138900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>22619100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>21575000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>21945200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>21264700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>21021000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>19682100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>19204700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>19329900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>19044800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>18495000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>18275000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>17244500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>16647500</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>3670700</v>
+      <c r="D60" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E60" s="3">
-        <v>10248700</v>
-      </c>
-      <c r="F60" s="3">
+        <v>22552000</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="3">
         <v>11710800</v>
       </c>
-      <c r="G60" s="3">
-        <v>9381600</v>
-      </c>
-      <c r="H60" s="3">
-        <v>20242600</v>
+      <c r="H60" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I60" s="3">
+        <v>7258100</v>
+      </c>
+      <c r="J60" s="3">
         <v>11043400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10074300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10547800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7313500</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5914,151 +6058,157 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>38285100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>36685500</v>
+        <v>33867400</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>38353200</v>
       </c>
-      <c r="G61" s="3">
-        <v>35703700</v>
-      </c>
       <c r="H61" s="3">
-        <v>32754200</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>38918400</v>
+      </c>
+      <c r="J61" s="3">
         <v>37838000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>36476800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>36489700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>41356500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>33794000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>31572800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>31785500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>29446700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>29889600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31374300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>31744800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>31339600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>31786500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>33212400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>37004500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>37701100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>37525700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>37410700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>37668500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>40229600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>37481900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>35869000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>34202200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>34591600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>35174700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>34962700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>35088200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>34193700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>34384900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>33751200</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>42793500</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3">
-        <v>34121300</v>
-      </c>
-      <c r="F62" s="3">
+        <v>24436600</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3">
         <v>35953600</v>
       </c>
-      <c r="G62" s="3">
-        <v>31643700</v>
-      </c>
-      <c r="H62" s="3">
-        <v>24633400</v>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I62" s="3">
+        <v>31453900</v>
+      </c>
+      <c r="J62" s="3">
         <v>35752500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>33269900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>34787700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>35535300</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6134,8 +6284,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6244,8 +6397,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6354,8 +6510,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6464,118 +6623,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
         <v>84749300</v>
       </c>
-      <c r="E66" s="3">
-        <v>81055500</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="3">
         <v>86264300</v>
       </c>
-      <c r="G66" s="3">
-        <v>76729000</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3">
         <v>81303000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>84862100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>80016200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>82031300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>87818900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>80219200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>72994800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>76355800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>73101400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>75179800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>77269700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>77428100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>74690500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>76131100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>79367500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>86642100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>88751200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>89592700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>87755300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>87183700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>89160100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>87832500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>83373800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>78716600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>79041800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>80311500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>79690300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>79485200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>77383600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>77218100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>74665300</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6614,8 +6779,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6724,8 +6890,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6834,8 +7003,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6944,8 +7116,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7054,8 +7229,11 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7063,109 +7241,112 @@
         <v>8</v>
       </c>
       <c r="E72" s="3">
-        <v>21598800</v>
-      </c>
-      <c r="F72" s="3">
+        <v>22403700</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3">
         <v>23579600</v>
       </c>
-      <c r="G72" s="3">
-        <v>20401500</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
         <v>21551200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>22515000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20971500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21213900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>22977200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21402300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18983000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19650300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19317900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>19625900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>20469500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>20268200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>19459100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>20219500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>21453300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>23117700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>24266800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>24561300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>24406600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>23503000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>24559200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>23318000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22550800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>21382600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>20930200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>20440400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>19935700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>19246400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>18427200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>17917900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>17520500</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7274,8 +7455,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7384,8 +7568,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7494,118 +7681,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
         <v>27311100</v>
       </c>
-      <c r="E76" s="3">
-        <v>25991300</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="3">
         <v>27237800</v>
       </c>
-      <c r="G76" s="3">
-        <v>25323200</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3">
         <v>26058400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>26442600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25181100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25198400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>26656900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23113400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21339900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22199700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21655800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21626500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22478300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>22399400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21471800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21537500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>23211700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>25037000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>26373700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>27406600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>27221500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>26445600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>27840900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>26597200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>26048900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>24653900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>24249100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>24117900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>23601100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>22829000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>22243300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>21616300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>20977200</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7714,233 +7907,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
         <v>533200</v>
       </c>
-      <c r="E81" s="3">
-        <v>565000</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3">
         <v>671600</v>
       </c>
-      <c r="G81" s="3">
-        <v>539200</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3">
         <v>839200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>646300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>436100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>435500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>589900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>636200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>385300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>417400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>669300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>444200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>587400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>479300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>357100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>353100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>341200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>426900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>514300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>775900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>826500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>634000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>841200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>766100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>697700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>726700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>513000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>817400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>689400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>811000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>497800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>665000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7979,118 +8181,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>340400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>674200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>623400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>590600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>412400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>687800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>561400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>583400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>688200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>661200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>543000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>553900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>554900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>567100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>595200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>600400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>568500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>592200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>607800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>656400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>708000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>673700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>696300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>678900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>745700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>706100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>672500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>643600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>698100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>625100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>610500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>596800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>583400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>562000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>551500</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8199,8 +8405,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8309,8 +8518,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8419,8 +8631,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8529,8 +8744,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8639,8 +8857,11 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8656,101 +8877,104 @@
       <c r="G89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>2094600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2380500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2638800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1361800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2508500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2248700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1879900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-214000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2243300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1184200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2698700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1608600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2407900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1732000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2631100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1552600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2834900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1711200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3255200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1636300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1980300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1020200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1637600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>884100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1772000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1193700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1172300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>803500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1250000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>994000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1888000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8789,8 +9013,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8806,101 +9031,104 @@
       <c r="G91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1657000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2075200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2252700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2221800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2280700</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-254596000</v>
       </c>
       <c r="N91" s="3">
         <v>-254596000</v>
       </c>
       <c r="O91" s="3">
+        <v>-254596000</v>
+      </c>
+      <c r="P91" s="3">
         <v>-223427000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-248094000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-229768000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-256101000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-39500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-42700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-84600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-133300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-79200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-172200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-116600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-62600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-48600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-106500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-127700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-198600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-147500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-155900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-197500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-222200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2642900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2149200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2170900</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9009,8 +9237,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9119,8 +9350,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9136,101 +9370,104 @@
       <c r="G94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1041600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2521100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3014300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2833300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3059900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1783200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1362800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1529700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-236300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2314500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2310200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-852200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2514400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3140600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1425100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2023400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3372700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3499800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3389900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3065100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1698000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3863100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2709000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>32500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-760600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1359900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>116900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1077700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1208800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-357200</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9269,8 +9506,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9286,101 +9524,104 @@
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>352500</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>347300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-359200</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-375400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-322600</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-385400</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-320100</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-439200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-408700</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-540100</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-363000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-454400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-312700</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-345000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-267500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9489,8 +9730,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9599,8 +9843,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9709,8 +9956,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9726,211 +9976,217 @@
       <c r="G100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>-217400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>128100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>286700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-784900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2776100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-190100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-271200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>933800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1715900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>192400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-205900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-350200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-356000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>131600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-216700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>852700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1587500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>927700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-136900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>197600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-769700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3671900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>352000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1637300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-330300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>571200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>434300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>622800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>713600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-108100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-426900</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>91300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-52300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>47100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>136900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>31200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-134900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>86300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>171700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>138400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-126300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>79700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>157300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>111600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>39900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>8600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>83400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-39400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>51700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-35300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-58100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-69800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>49100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>10000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-82800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>24000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>42100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>41400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>141000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-42500</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9947,96 +10203,99 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>927000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-64800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-41800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2119500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2255900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>149100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>325600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-652600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>402700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-898100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>186600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>414800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-379100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1277400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>989800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>383500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1010300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-809300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-306900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1289300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-496100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>759200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-670400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-710700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>798800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>424100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-166800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1487500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>874100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-181900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1061400</v>
       </c>
     </row>
